--- a/audits/aquaphor/aquaphor_audit.xlsx
+++ b/audits/aquaphor/aquaphor_audit.xlsx
@@ -527,38 +527,50 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Caprylic/Capric Triglyceride</t>
+          <t>Water, Glycerin, Caprylic/Capric Triglyceride, Cetyl Alcohol, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Cetyl Palmitate, Glyceryl Stearate SE, Glyceryl Stearate, Tapioca Starch, Panthenol, Bisabolol, Tocopherol, Sodium Hyaluronate, Cholesterol, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, Pantalactone, Carrageenan, Xanthan Gum, Pentylene Glycol, Hydrogenated Castor Oil, Caprylyl Glycol, Sodium Cetearyl Sulfate, Phenoxyethanol, Sodium Citrate, Citric Acid.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Pentylene Glycol [1,2] / Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Caprylic/Capric Triglyceride</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Water, Glycerin, Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Pantalactone, Carrageenan</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>3 flagged ingredient(s): Pentylene Glycol, Sodium Cetearyl Sulfate, Phenoxyethanol. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Water, Glycerin, Caprylic/Capric Triglyceride.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444). Brand site showed partial list only: Water, Glycerin, Caprylic/Capric Triglyceride. Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -585,38 +597,50 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Cetearyl Alcohol</t>
+          <t>Water, Glycerin, Cetearyl Alcohol, Ethylhexyl Stearate, Glyceryl Stearate SE, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Panthenol, Bisabolol, Tocopherol, Sodium Hyaluronate, Cholesterol, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, Pantalactone, Ricinus Communis (Castor) Seed Oil, Cetyl Alcohol, Hydroxypropyl Starch Phosphate, Sodium Cetearyl Sulfate, Ethylhexylglycerin, Phenoxyethanol, Sodium Citrate, Citric Acid.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Water, Glycerin</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Pantalactone, Hydroxypropyl Starch Phosphate</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>3 flagged ingredient(s): Sodium Cetearyl Sulfate, Ethylhexylglycerin, Phenoxyethanol. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Water, Glycerin.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998). Brand site showed partial list only: Water, Glycerin, Cetearyl Alcohol. Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -643,38 +667,50 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Cetearyl Alcohol</t>
+          <t>Water, Glycerin, Cetearyl Alcohol, Ethylhexyl Stearate, Glyceryl Stearate SE, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Panthenol, Bisabolol, Tocopherol, Sodium Hyaluronate, Cholesterol, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, Pantalactone, Ricinus Communis (Castor) Seed Oil, Cetyl Alcohol, Hydroxypropyl Starch Phosphate, Sodium Cetearyl Sulfate, Ethylhexylglycerin, Phenoxyethanol, Sodium Citrate, Citric Acid.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Water, Glycerin</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Pantalactone, Hydroxypropyl Starch Phosphate</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>3 flagged ingredient(s): Sodium Cetearyl Sulfate, Ethylhexylglycerin, Phenoxyethanol. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Water, Glycerin.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953). Brand site showed partial list only: Water, Glycerin, Cetearyl Alcohol. Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -701,38 +737,50 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Cetearyl Alcohol</t>
+          <t>Water, Glycerin, Cetearyl Alcohol, Ethylhexyl Stearate, Glyceryl Stearate SE, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Panthenol, Bisabolol, Tocopherol, Sodium Hyaluronate, Cholesterol, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, Pantalactone, Ricinus Communis (Castor) Seed Oil, Cetyl Alcohol, Hydroxypropyl Starch Phosphate, Sodium Cetearyl Sulfate, Ethylhexylglycerin, Phenoxyethanol, Sodium Citrate, Citric Acid.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Water, Glycerin</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Pantalactone, Hydroxypropyl Starch Phosphate</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>3 flagged ingredient(s): Sodium Cetearyl Sulfate, Ethylhexylglycerin, Phenoxyethanol. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Water, Glycerin.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924). Brand site showed partial list only: Water, Glycerin, Cetearyl Alcohol. Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -780,12 +828,12 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>Provisional (brand-site partial list only).</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Water, Glycerin, Caprylic/Capric Triglyceride.</t>
+          <t>Provisional: tier from brand-site partial list only. no retailer INCI found. Walmart Aquaphor Moisturizing Cream listings are 8 oz and 16 oz only. Not used.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -817,38 +865,50 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Caprylic/Capric Triglyceride</t>
+          <t>Water, Glycerin, Caprylic/Capric Triglyceride, Cetyl Alcohol, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Cetyl Palmitate, Glyceryl Stearate SE, Glyceryl Stearate, Tapioca Starch, Panthenol, Bisabolol, Tocopherol, Sodium Hyaluronate, Cholesterol, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, Pantalactone, Carrageenan, Xanthan Gum, Pentylene Glycol, Hydrogenated Castor Oil, Caprylyl Glycol, Sodium Cetearyl Sulfate, Phenoxyethanol, Sodium Citrate, Citric Acid.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pentylene Glycol [1,2] / Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Caprylic/Capric Triglyceride</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>Water, Glycerin, Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Pantalactone, Carrageenan</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>3 flagged ingredient(s): Pentylene Glycol, Sodium Cetearyl Sulfate, Phenoxyethanol. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Water, Glycerin, Caprylic/Capric Triglyceride.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701). Brand site showed partial list only: Water, Glycerin, Caprylic/Capric Triglyceride. Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride).</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -875,7 +935,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Octyldodecanol, Ricinus Communis Seed Oil, Butyrospermum Parkii (Shea) Butter</t>
+          <t>Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Beeswax, Helianthus Annuus (Sunflower) Seed Wax, Glycerin, Hydrogenated Castor Oil, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Aloe Barbadensis Leaf Juice Powder, Panthenol, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Tocopherol, Ascorbyl Palmitate, Water. 1% skin safe synthetic ingredients: Ascorbyl Palmitate, Panthenol, Pantolactone, Tocopherol, Sodium Citrate, Citric Acid.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -890,23 +950,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Octyldodecanol</t>
+          <t>Octyldodecanol, Glycerin, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Ascorbyl Palmitate, Water, Pantolactone</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>No flagged ingredients in the full list per reference.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Octyldodecanol.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Aloe-Vera-0-17-oz-Stick/5322031840). Brand site showed partial list only: Octyldodecanol, Ricinus Communis Seed Oil, Butyrospermum Parkii (Shea) Butter. Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Aloe Vera, 0.17 oz' (single stick). Cross-check: first three match brand site. Brand-site list named Ricinus Communis Seed Oil; retailer uses Ricinus Communis (Castor) Seed Oil, same ingredient.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -933,7 +993,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Octyldodecanol, Ricinus Communis Seed Oil, Butyrospermum Parkii (Shea) Butter</t>
+          <t>Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Beeswax, Helianthus Annuus (Sunflower) Seed Wax, Cocos Nucifera (Coconut) Oil, Hydrogenated Castor Oil, Panthenol, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Tocopherol, Ascorbyl Palmitate, Water, Pantolactone, Citric Acid. Synthetics: Ascorbyl Palmitate, Panthenol, Pantolactone, Tocopherol, Citric Acid</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -948,23 +1008,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Octyldodecanol</t>
+          <t>Octyldodecanol, Ascorbyl Palmitate, Water, Pantolactone</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>No flagged ingredients in the full list per reference.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Octyldodecanol.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Coconut-Oil-0-17-oz-Stick/5415018384). Brand site showed partial list only: Octyldodecanol, Ricinus Communis Seed Oil, Butyrospermum Parkii (Shea) Butter. Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Coconut Oil, 0.17 oz' (single stick). Cross-check: first three match brand site.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -991,7 +1051,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrolatum (41%)</t>
+          <t>Active Ingredients: Petrolatum (41%). Inactive Ingredients: Mineral Oil, Ceresin, Lanolin alcohol, Panthenol, Glycerin, Bisabolol.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1000,15 +1060,23 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin alcohol, Glycerin</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -1016,17 +1084,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069). Brand site showed partial list only: Petrolatum (41%). Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zinc Oxide (40%)</t>
+          <t>Active Ingredient: Zinc Oxide 40.0%...Purpose: Skin Protectant Ointment. Inactive Ingredients: Glycerin, Caprylic/Capric Triglyceride, Octyldodecanol, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Panthenol, Butyrospermum Parkii (Shea) Butter, Water.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1066,21 +1134,25 @@
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Glycerin, Caprylic/Capric Triglyceride, Octyldodecanol, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Water</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>No flagged ingredients in the full list per reference.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown. Zinc oxide graded as reference entry 'zinc oxide (non-nano)' (low tox in creams). Nano status not stated on page.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Diaper-Rash-Paste-Maximum-Strength-40-Zinc-Oxide-Diaper-Rash-Cream-Diaper-Rash-Ointment-3-5-oz/299965693). Brand site showed partial list only: Zinc Oxide (40%). Walmart listing 'Aquaphor Baby Diaper Rash Paste, Maximum Strength 40% Zinc Oxide, 3.5 oz'. Cross-check: brand-site Zinc Oxide (40%) matches the active.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1107,38 +1179,46 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Octyldodecanol, Ricinus Communis Seed Oil, Beeswax</t>
+          <t>Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Beeswax, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Panthenol, Dimethicone, Water, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Tocopherol, Ascorbyl Palmitate</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Dimethicone [2,6]</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Octyldodecanol</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>Octyldodecanol, Bis-Diglyceryl Polyacyladipate-2, Water, Tocopheryl Acetate, Ascorbyl Palmitate</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>PFAS</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>1 flagged ingredient(s): Dimethicone. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Octyldodecanol.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/621710698). Brand site showed partial list only: Octyldodecanol, Ricinus Communis Seed Oil, Beeswax. Walmart listing 'Aquaphor Lip Repair Balm Stick for Dry Chapped Lips with Shea Butter, 0.17 oz'. Cross-check: first three match brand site. Dimethicone appears in this retailer list but not in the brand-site partial list; flagged for grader.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1165,38 +1245,46 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Avobenzone (3%), Homosalate (9%), Octisalate (4.5%), Octocrylene (9%)</t>
+          <t>Active Ingredients: Avobenzone (3 %), Sunscreen; Homosalate (9 %), Sunscreen; Octisalate (4.5 %), Sunscreen; Octocrylene (9 %), Sunscreen. Inactive Ingredients: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Beeswax, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Cetearyl Alcohol, Dimethicone, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, Helianthus Annus (Sunflower) Seed Oil, Tocopherol.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Dimethicone [2,6]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Octyldodecanol, Bis-Diglyceryl Polyacyladipate-2, Tocopheryl Acetate, Ascorbyl Palmitate</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>PFAS</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) on displayed list: Avobenzone, Homosalate, Octisalate, Octocrylene.</t>
+          <t>5 flagged ingredient(s): Avobenzone, Homosalate, Octisalate, Octocrylene.... Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown. Classified as sunscreen (contains UV filters).</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Spf-30/1370153078). Brand site showed partial list only: Avobenzone (3%), Homosalate (9%), Octisalate (4.5%), Octocrylene (9%). Walmart listing 'Aquaphor Broad Spectrum SPF 30 Lip Repair Stick + Sunscreen 0.17 oz'. Cross-check: actives Avobenzone, Homosalate, Octisalate, Octocrylene match brand site.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1336,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s) on displayed list: Petrolatum, Avobenzone, Octinoxate, Octisalate.... Escalation: carcinogen in leave-on.</t>
+          <t>Provisional (brand-site partial list only).</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Escalated: petrolatum (cat. 1) in a leave-on product (sunscreen lip product). Tier raised per rubric. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown. Classified as sunscreen (contains UV filters).</t>
+          <t>Provisional: tier from brand-site partial list only. no retailer INCI found yet. The single Lip Protectant + SPF 30 (0.35 oz tube) matched on Walmart; no Dual Pack listing with matching actives located on Walmart or Target search. Not used.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1285,38 +1373,46 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Avobenzone (3%), Homosalate (9%), Octisalate (4.5%), Octocrylene (9%)</t>
+          <t>Active Ingredients: Avobenzone 3%, Homosalate 9%, Octisalate 4.5%, Octocrylene 9%. Other Ingredients: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Beeswax, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Cetearyl Alcohol, Dimethicone, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, Helianthus Annuus (Sunflower) Seed Oil, Tocopherol.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2]</t>
+          <t>Avobenzone [2] / Homosalate [2] / Octisalate [2] / Octocrylene [2] / Dimethicone [2,6]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Octyldodecanol, Bis-Diglyceryl Polyacyladipate-2, Tocopheryl Acetate, Ascorbyl Palmitate</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>PFAS</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) on displayed list: Avobenzone, Homosalate, Octisalate, Octocrylene.</t>
+          <t>5 flagged ingredient(s): Avobenzone, Homosalate, Octisalate, Octocrylene.... Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown. Classified as sunscreen (contains UV filters).</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Protect-SPF-30-Stick-Dual-Pack-0-34oz-Pack-of-2-sticks/15665510241). Brand site showed partial list only: Avobenzone (3%), Homosalate (9%), Octisalate (4.5%), Octocrylene (9%). Walmart listing 'Aquaphor Lip Repair &amp; Protect SPF 30 Stick, 2pk, 0.35oz, Clear'. Cross-check: actives match brand site (Avobenzone 3, Homosalate 9, Octisalate 4.5, Octocrylene 9). Retailer 2-pack title, same product.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1439,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Petrolatum (41%)</t>
+          <t>Active: Petrolatum (41%)...Purpose: Skin Protectant (Ointment). Inactive: Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1352,15 +1448,23 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -1368,17 +1472,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1509,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis Seed Oil</t>
+          <t>Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Glycerin, Bis-Diglyceryl Polyacyladipate-2, Panthenol, Water, Polyglyceryl-3 Diisostearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Bisabolol, Sodium Ascorbyl Phosphate, Lecithin, Tocopherol, Ascorbyl Palmitate, Beeswax, C20-40 Alkyl Stearate, Magnesium Stearate, Magnesium Sulfate, Glyceryl Stearate, Glyceryl Oleate, Citric Acid</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1417,26 +1521,30 @@
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate</t>
+          <t>Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Caprylic/Capric Triglyceride, Glycerin, Bis-Diglyceryl Polyacyladipate-2, Water, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Lecithin, Ascorbyl Palmitate, C20-40 Alkyl Stearate, Magnesium Stearate, Glyceryl Stearate</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>No flagged ingredients in the full list per reference.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970). Brand site showed partial list only: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis Seed Oil. Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1463,38 +1571,46 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Octyldodecanol, Ricinus Communis Seed Oil, Beeswax</t>
+          <t>Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Beeswax, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Panthenol, Dimethicone, Water, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Tocopherol, Ascorbyl Palmitate</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Dimethicone [2,6]</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Octyldodecanol</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>Octyldodecanol, Bis-Diglyceryl Polyacyladipate-2, Water, Tocopheryl Acetate, Ascorbyl Palmitate</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PFAS</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>1 flagged ingredient(s): Dimethicone. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Octyldodecanol.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/304762780). Brand site showed partial list only: Octyldodecanol, Ricinus Communis Seed Oil, Beeswax. Walmart listing 'Aquaphor, Lip Repair Balm Stick, 0.17 oz, 2 Pack for Dry Chapped Lips'. Cross-check: first three match brand site. Same printed list as the single Lip Repair Stick. Dimethicone appears in retailer list only.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1637,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Petrolatum (30%)</t>
+          <t>Active ingredients: Petrolatum 30% (Purpose: Skin Protectant)... Inactive ingredients: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Beeswax, Butyrospermum Parkii (Shea) Butter, Tocopherol, Panthenol, Glycerin, Bisabolol.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1537,8 +1653,16 @@
           <t>Petrolatum [1]</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Caprylic/Capric Triglyceride, Glycerin</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -1546,17 +1670,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>1 flagged ingredient(s): Petrolatum. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860). Brand site showed partial list only: Petrolatum (30%). Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1583,42 +1707,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate</t>
+          <t>Water, Decyl Glucoside, Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine, Panthenol, Bisabolol, Polyquaternium-10, Sea Salt, Citric Acid, Sodium Chloride, Sodium Benzoate.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>Avoid (Mild)</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>PEG-200 Hydrogenated Glyceryl Palmate [inferred: PEG-] [1,2,4,5]</t>
+          <t>Sodium Myreth Sulfate [inferred: sulfate] [1,4,5] / PEG-200 Hydrogenated Glyceryl Palmate [inferred: PEG-] [1,2,4,5] / Cocamidopropyl Betaine [1,4] / Bisabolol [4]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Water, Polyquaternium-10, Sea Salt</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: PEG-200 Hydrogenated Glyceryl Palmate.</t>
+          <t>4 flagged ingredient(s): Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine, Bisabolol.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. PEG-200 Hydrogenated Glyceryl Palmate flagged by PEG- naming pattern (inferred; not in reference). Unknown to reference (manual review): Water.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-and-Shampoo-Unscented-Baby-Shampoo-and-Wash-25-4-Fl-Oz-Pump-Bottle/5032877839). Brand site showed partial list only: Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate. Walmart listing 'Aquaphor Baby Wash &amp; Shampoo, Fragrance Free and Tear Free, 25.4 fl oz'. Cross-check: first three (Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate) match brand site. Panel text was read from the listing's collapsible Ingredients block; ancestry check was inconclusive, so re-verify this row if Nina wants a second look. Sodium Myreth Sulfate is a sulfate and is flagged by the grader.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1645,38 +1769,46 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Cetearyl Alcohol</t>
+          <t>Water, Glycerin, Cetearyl Alcohol, Ethylhexyl Stearate, Glyceryl Stearate SE, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Panthenol, Cetyl Alcohol, Hydroxypropyl Starch Phosphate, Tocopherol, Sodium Hyaluronate, Pantolactone, Ceramide NP, Cholesterol, Phytosphingosine, Oleic Acid, Glycine Soja (Soybean) Oil, Phenoxyethanol, Sodium Citrate, Sodium Cetearyl Sulfate, Ethylhexylglycerin, Citric Acid.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Ethylhexylglycerin [4,5]</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Water, Glycerin</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>3 flagged ingredient(s): Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Water, Glycerin.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Lotion-3oz/19974261109). Brand site showed partial list only: Water, Glycerin, Cetearyl Alcohol. Walmart listing 'Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 fl oz'. Cross-check: first three match brand site.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1703,38 +1835,46 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Cetearyl Alcohol</t>
+          <t>Water, Glycerin, Cetearyl Alcohol, Ethylhexyl Stearate, Glyceryl Stearate SE, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Panthenol, Cetyl Alcohol, Hydroxypropyl Starch Phosphate, Tocopherol, Sodium Hyaluronate, Pantolactone, Ceramide NP, Cholesterol, Phytosphingosine, Oleic Acid, Glycine Soja (Soybean) Oil, Phenoxyethanol, Sodium Citrate, Sodium Cetearyl Sulfate, Ethylhexylglycerin, Citric Acid.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Ethylhexylglycerin [4,5]</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Water, Glycerin</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>3 flagged ingredient(s): Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Water, Glycerin.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Daily-Lotion-8-oz/19736656895). Brand site showed partial list only: Water, Glycerin, Cetearyl Alcohol. Walmart listing 'Aquaphor, Baby Sensitive Lotion, Baby Lotion, 8 fl oz'. Cross-check: first three match brand site (Water, Glycerin, Cetearyl Alcohol).</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1901,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Petrolatum (41%)</t>
+          <t>Active Ingredients: Petrolatum (41%)...Purpose: Skin Protectant (Ointment). Inactive Ingredients: Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1770,15 +1910,23 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -1786,17 +1934,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1971,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Petrolatum (41%)</t>
+          <t>Active Ingredients: Petrolatum (41%). Inactive Ingredients: Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1832,15 +1980,23 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -1848,17 +2004,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1902,12 +2058,12 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>Provisional (brand-site partial list only).</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown. Zinc oxide graded as reference entry 'zinc oxide (non-nano)' (low tox in creams). Nano status not stated on page.</t>
+          <t>Provisional: tier from brand-site partial list only. variant mismatch. Walmart Aquaphor Diaper Rash Cream listings are 3.5 oz only. The brand list says 3 oz. Not used.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1939,7 +2095,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Petrolatum (31%), Avobenzone (3%), Octinoxate (6.75%), Octisalate (4.5%), Octocrylene (2%), Oxybenzone (5.4%)</t>
+          <t>Active: Petrolatum 31.0%...Purpose: Skin Protectant, Avobenzone 3.0%...Purpose: Sunscreen, Octinoxate 6.75%...Purpose: Sunscreen, Octisalate 4.5%...Purpose: Sunscreen, Octocrylene 2.0%...Purpose: Sunscreen, Oxybenzone 5.4%...Purpose: Sunscreen. Inactive: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Glycerin, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Panthenol, Water, Polyglyceryl-3 Diisostearate, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, Beeswax, C20-40 Alkyl Stearate, Magnesium Sulfate, Magnesium Stearate, BHT.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1948,15 +2104,19 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Avobenzone [2] / Octinoxate [2] / Octisalate [2] / Octocrylene [2] / Oxybenzone [2]</t>
+          <t>Petrolatum [1] / Avobenzone [2] / Octinoxate [2] / Octisalate [2] / Octocrylene [2] / Oxybenzone [2] / BHT [inferred: BHT] [1,2]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Glycerin, Caprylic/Capric Triglyceride, Water, Tocopheryl Acetate, C20-40 Alkyl Stearate, Magnesium Stearate</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -1964,17 +2124,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>6 flagged ingredient(s) on displayed list: Petrolatum, Avobenzone, Octinoxate, Octisalate.... Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s): Petrolatum, Avobenzone, Octinoxate, Octisalate.... Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Escalated: petrolatum (cat. 1) in a leave-on product (sunscreen lip product). Tier raised per rubric. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown. Classified as sunscreen (contains UV filters).</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Lip-Balm-with-Sunscreen-Lip-Balm-SPF-30-0-35-Oz-Tube/23623346). Brand site showed partial list only: Petrolatum (31%), Avobenzone (3%), Octinoxate (6.75%), Octisalate (4.5%), Octocrylene (2%), Oxybenzone (5.4%). Walmart listing 'Aquaphor, Lip Repair Lip Balm with Sunscreen, SPF 30, 0.35 fl oz' (tube). Cross-check: all six actives match brand-site values exactly.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2161,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis Seed Oil</t>
+          <t>Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Glycerin, Panthenol, Bis-Diglyceryl Polyacyladipate-2, Water, Polyglyceryl-3 Diisostearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopherol, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Bisabolol, Beeswax, C20-40 Alkyl Stearate, Magnesium Stearate, Magnesium Sulfate</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2013,26 +2173,30 @@
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate</t>
+          <t>Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Caprylic/Capric Triglyceride, Glycerin, Bis-Diglyceryl Polyacyladipate-2, Water, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, C20-40 Alkyl Stearate, Magnesium Stearate</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>No flagged ingredients in the full list per reference.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Unknown to reference (manual review): Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721). Brand site showed partial list only: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis Seed Oil. Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2223,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Petrolatum (41%)</t>
+          <t>Active: Petrolatum 41%...Purpose: Skin Protectant (Ointment) Treatment or Prevention of Diaper Rash. Inactive: Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2068,15 +2232,23 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -2084,17 +2256,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2293,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Petrolatum (41%)</t>
+          <t>Active ingredient: Petrolatum 41%; Purpose: Skin Protectant. Inactive ingredients: Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2130,15 +2302,23 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -2146,17 +2326,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2183,42 +2363,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate</t>
+          <t>Water, Decyl Glucoside, Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine, Panthenol, Bisabolol, Polyquaternium-10, Sea Salt, Citric Acid, Sodium Chloride, Sodium Benzoate.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>Avoid (Mild)</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>PEG-200 Hydrogenated Glyceryl Palmate [inferred: PEG-] [1,2,4,5]</t>
+          <t>Sodium Myreth Sulfate [inferred: sulfate] [1,4,5] / PEG-200 Hydrogenated Glyceryl Palmate [inferred: PEG-] [1,2,4,5] / Cocamidopropyl Betaine [1,4] / Bisabolol [4]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Water, Polyquaternium-10, Sea Salt</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: PEG-200 Hydrogenated Glyceryl Palmate.</t>
+          <t>4 flagged ingredient(s): Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine, Bisabolol.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. PEG-200 Hydrogenated Glyceryl Palmate flagged by PEG- naming pattern (inferred; not in reference). Unknown to reference (manual review): Water.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301). Brand site showed partial list only: Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate. Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2425,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Butane, Petrolatum, Mineral Oil</t>
+          <t>Butane, Petrolatum, Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2261,10 +2441,14 @@
           <t>Petrolatum [1] / Mineral Oil [1]</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Butane</t>
+          <t>Butane, Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2274,17 +2458,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) on displayed list: Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Aerosol spray format; reference spray conditionals not triggered by listed ingredients. Unknown to reference (manual review): Butane.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182). Brand site showed partial list only: Butane, Petrolatum, Mineral Oil. Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2495,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Petrolatum (41%)</t>
+          <t>Active Ingredients: Petrolatum 41%...Purpose: Skin Protectant (Ointment)/Treatment or Prevention of Diaper Rash. Inactive Ingredients: Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol Glycerin, Bisabolol</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2320,15 +2504,23 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -2336,17 +2528,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2565,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrolatum (41%)</t>
+          <t>Active Ingredients: Petrolatum (41%)...Purpose: Skin Protectant (Ointment). Inactive Ingredients: Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2382,15 +2574,23 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -2398,17 +2598,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2435,38 +2635,50 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hydrocortisone (1%)</t>
+          <t>Active ingredients: Hydrocortisone 1% (Purpose: Anti-Itch Ointment)... Inactive ingredients: Petrolatum, Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol, Menthoxypropanediol.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Hydrocortisone</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>Hydrocortisone, Ceresin, Lanolin Alcohol, Glycerin, Menthoxypropanediol</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown. Unknown to reference (manual review): Hydrocortisone.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819). Brand site showed partial list only: Hydrocortisone (1%). Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2518,12 +2730,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>Provisional (brand-site partial list only).</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Provisional: tier from brand-site partial list only. no retailer INCI found on Walmart. The Aquaphor Healing Balm Stick 0.65 oz (Pack of 3) listing shows no Ingredients block. Retry elsewhere.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2576,12 +2788,12 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>Provisional (brand-site partial list only).</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Displayed list is three ingredients only. Unknown to reference (manual review): Water, Glycerin, Urea.</t>
+          <t>Provisional: tier from brand-site partial list only. no retailer INCI found. Walmart (1-pair hand mask) and Target (Advanced Therapy Repairing Hand Mask 0.7 fl oz) listings show no printed Ingredients block for the product. Not used.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2634,12 +2846,12 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the displayed list per reference.</t>
+          <t>Provisional (brand-site partial list only).</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Displayed list is three ingredients only. Unknown to reference (manual review): Water, Glycerin, Urea.</t>
+          <t>Provisional: tier from brand-site partial list only. no retailer INCI found. Walmart (1-pair foot mask) listing has no printed Aquaphor Ingredients block. Target listing for Advanced Therapy Repairing Foot Mask 0.7 fl oz exists but its ingredients were not visible. Not used.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2671,7 +2883,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Petrolatum (41%)</t>
+          <t>Active: Petrolatum (41%)...Purpose: Skin Protectant (Ointment). Inactive: Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2680,15 +2892,23 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -2696,17 +2916,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2762,12 +2982,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) on displayed list: Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>Provisional (brand-site partial list only).</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Aerosol spray format; reference spray conditionals not triggered by listed ingredients. Unknown to reference (manual review): Butane.</t>
+          <t>Provisional: tier from brand-site partial list only. variant mismatch / no retailer INCI found. Walmart lists the Aquaphor Ointment Body Spray in 3.7 oz and multipacks only. The 3.7 oz row is used for the 3.7 oz product; 6.2 oz not located.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2799,7 +3019,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Petrolatum (41%)</t>
+          <t>Active: Petrolatum (41%)...Purpose: Skin Protectant (Ointment). Inactive: Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2808,15 +3028,23 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -2824,17 +3052,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2886,12 +3114,12 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>Provisional (brand-site partial list only).</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Provisional: tier from brand-site partial list only. variant mismatch / no retailer INCI found. Walmart search for a 2 x 3.5 oz Aquaphor Healing Ointment returned only Baby Diaper Rash Paste 3.5 oz 2-pack and 1.75 oz travel packs. Not used.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -2923,7 +3151,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Petrolatum (41%)</t>
+          <t>Active Ingredients: Petrolatum (41%). Inactive Ingredients: Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol.</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2932,15 +3160,23 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>Petrolatum [1] / Mineral Oil [1]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Bisabolol [4,8]</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -2948,17 +3184,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) on displayed list: Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Brand page shows only this ingredient text (first names or the active-ingredient list); no full INCI list is on the page. Tier is provisional. Page label is 'Active Ingredients' (drug-label format); inactive ingredients are not shown.</t>
+          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>

--- a/audits/aquaphor/aquaphor_audit.xlsx
+++ b/audits/aquaphor/aquaphor_audit.xlsx
@@ -415,22 +415,6 @@
   </sheetPr>
   <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -536,21 +520,17 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pentylene Glycol [1,2] / Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Phenoxyethanol [1,2,4,5,8]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Bisabolol [4] (natural component, no source essential oil listed: full flag) / Pentylene Glycol [1,2] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Pantalactone, Carrageenan</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Tapioca Starch, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -560,12 +540,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s): Pentylene Glycol, Sodium Cetearyl Sulfate, Phenoxyethanol. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Pentylene Glycol, Sodium Cetearyl Sulfate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444). Brand site showed partial list only: Water, Glycerin, Caprylic/Capric Triglyceride. Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'. Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (16oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -606,21 +586,17 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Bisabolol [4] (natural component, no source essential oil listed: full flag) / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Pantalactone, Hydroxypropyl Starch Phosphate</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -630,12 +606,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s): Sodium Cetearyl Sulfate, Ethylhexylglycerin, Phenoxyethanol. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998). Brand site showed partial list only: Water, Glycerin, Cetearyl Alcohol. Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -676,21 +652,17 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Bisabolol [4] (natural component, no source essential oil listed: full flag) / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Pantalactone, Hydroxypropyl Starch Phosphate</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -700,12 +672,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s): Sodium Cetearyl Sulfate, Ethylhexylglycerin, Phenoxyethanol. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953). Brand site showed partial list only: Water, Glycerin, Cetearyl Alcohol. Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -746,21 +718,17 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Bisabolol [4] (natural component, no source essential oil listed: full flag) / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Pantalactone, Hydroxypropyl Starch Phosphate</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -770,12 +738,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s): Sodium Cetearyl Sulfate, Ethylhexylglycerin, Phenoxyethanol. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924). Brand site showed partial list only: Water, Glycerin, Cetearyl Alcohol. Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Moisturizing Cream (1.89oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -807,38 +775,46 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Caprylic/Capric Triglyceride</t>
+          <t>Water, Glycerin, Cetearyl Alcohol, Ethylhexyl Stearate, Glyceryl Stearate SE, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Panthenol, Bisabolol, Tocopherol, Sodium Hyaluronate, Cholesterol, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, Pantalactone, Ricinus Communis (Castor) Seed Oil, Cetyl Alcohol, Hydroxypropyl Starch Phosphate, Sodium Cetearyl Sulfate, Ethylhexylglycerin, Phenoxyethanol, Sodium Citrate, Citric Acid.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bisabolol [4] (natural component, no source essential oil listed: full flag) / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / Ethylhexylglycerin [4,5] / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Caprylic/Capric Triglyceride</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Provisional (brand-site partial list only).</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Provisional: tier from brand-site partial list only. no retailer INCI found. Walmart Aquaphor Moisturizing Cream listings are 8 oz and 16 oz only. Not used.</t>
+          <t>Audit notes: CONFLICT: CVS ingredients page (Aquaphor Moisturizing Cream, 1.89 OZ, prodid 923320) lists Water, Glycerin, Cetearyl Alcohol as the first three; brand site text lists Water, Glycerin, Caprylic/Capric Triglyceride. Both texts kept (brand_site_text unchanged). Grading uses the CVS verbatim list. Variant matches on name and size. Note the brand text may refer to a different formula or size. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.). Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-moisturizing-cream-1-89-oz-prodid-923320.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -874,21 +850,17 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pentylene Glycol [1,2] / Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Phenoxyethanol [1,2,4,5,8]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Bisabolol [4] (natural component, no source essential oil listed: full flag) / Pentylene Glycol [1,2] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Pantalactone, Carrageenan</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Tapioca Starch, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -898,12 +870,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s): Pentylene Glycol, Sodium Cetearyl Sulfate, Phenoxyethanol. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Pentylene Glycol, Sodium Cetearyl Sulfate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701). Brand site showed partial list only: Water, Glycerin, Caprylic/Capric Triglyceride. Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride).</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride). Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (8oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -950,18 +922,18 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Octyldodecanol, Glycerin, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Ascorbyl Palmitate, Water, Pantolactone</t>
+          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Aloe Barbadensis Leaf Juice Powder, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the full list per reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 9 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Aloe-Vera-0-17-oz-Stick/5322031840). Brand site showed partial list only: Octyldodecanol, Ricinus Communis Seed Oil, Butyrospermum Parkii (Shea) Butter. Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Aloe Vera, 0.17 oz' (single stick). Cross-check: first three match brand site. Brand-site list named Ricinus Communis Seed Oil; retailer uses Ricinus Communis (Castor) Seed Oil, same ingredient.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Aloe Vera, 0.17 oz' (single stick). Cross-check: first three match brand site. Brand-site list named Ricinus Communis Seed Oil; retailer uses Ricinus Communis (Castor) Seed Oil, same ingredient. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Aloe-Vera-0-17-oz-Stick/5322031840.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1008,18 +980,18 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Octyldodecanol, Ascorbyl Palmitate, Water, Pantolactone</t>
+          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Cocos Nucifera (Coconut) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the full list per reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 8 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Coconut-Oil-0-17-oz-Stick/5415018384). Brand site showed partial list only: Octyldodecanol, Ricinus Communis Seed Oil, Butyrospermum Parkii (Shea) Butter. Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Coconut Oil, 0.17 oz' (single stick). Cross-check: first three match brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Coconut Oil, 0.17 oz' (single stick). Cross-check: first three match brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Coconut-Oil-0-17-oz-Stick/5415018384.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1060,21 +1032,17 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin alcohol</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1084,12 +1052,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069). Brand site showed partial list only: Petrolatum (41%). Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant.</t>
+          <t>Audit notes: Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1136,18 +1104,18 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Glycerin, Caprylic/Capric Triglyceride, Octyldodecanol, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Water</t>
+          <t>unknown — manual review needed: Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Butyrospermum Parkii (Shea) Butter</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the full list per reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 3 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Diaper-Rash-Paste-Maximum-Strength-40-Zinc-Oxide-Diaper-Rash-Cream-Diaper-Rash-Ointment-3-5-oz/299965693). Brand site showed partial list only: Zinc Oxide (40%). Walmart listing 'Aquaphor Baby Diaper Rash Paste, Maximum Strength 40% Zinc Oxide, 3.5 oz'. Cross-check: brand-site Zinc Oxide (40%) matches the active.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Diaper Rash Paste, Maximum Strength 40% Zinc Oxide, 3.5 oz'. Cross-check: brand-site Zinc Oxide (40%) matches the active. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Diaper-Rash-Paste-Maximum-Strength-40-Zinc-Oxide-Diaper-Rash-Cream-Diaper-Rash-Ointment-3-5-oz/299965693.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1198,7 +1166,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Octyldodecanol, Bis-Diglyceryl Polyacyladipate-2, Water, Tocopheryl Acetate, Ascorbyl Palmitate</t>
+          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1208,12 +1176,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s): Dimethicone. Escalation: PFAS.</t>
+          <t>1 flagged ingredient(s) in the printed list (Dimethicone); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/621710698). Brand site showed partial list only: Octyldodecanol, Ricinus Communis Seed Oil, Beeswax. Walmart listing 'Aquaphor Lip Repair Balm Stick for Dry Chapped Lips with Shea Butter, 0.17 oz'. Cross-check: first three match brand site. Dimethicone appears in this retailer list but not in the brand-site partial list; flagged for grader.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Balm Stick for Dry Chapped Lips with Shea Butter, 0.17 oz'. Cross-check: first three match brand site. Dimethicone appears in this retailer list but not in the brand-site partial list; flagged for grader. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick (Dual Pack). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/621710698.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1264,7 +1232,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Octyldodecanol, Bis-Diglyceryl Polyacyladipate-2, Tocopheryl Acetate, Ascorbyl Palmitate</t>
+          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Ascorbyl Palmitate, helianthus annuus (sunflower) seed oil</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1274,12 +1242,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s): Avobenzone, Homosalate, Octisalate, Octocrylene.... Escalation: PFAS.</t>
+          <t>5 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Spf-30/1370153078). Brand site showed partial list only: Avobenzone (3%), Homosalate (9%), Octisalate (4.5%), Octocrylene (9%). Walmart listing 'Aquaphor Broad Spectrum SPF 30 Lip Repair Stick + Sunscreen 0.17 oz'. Cross-check: actives Avobenzone, Homosalate, Octisalate, Octocrylene match brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Broad Spectrum SPF 30 Lip Repair Stick + Sunscreen 0.17 oz'. Cross-check: actives Avobenzone, Homosalate, Octisalate, Octocrylene match brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Spf-30/1370153078.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1311,7 +1279,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Petrolatum (31%), Avobenzone (3%), Octinoxate (6.75%), Octisalate (4.5%), Octocrylene (2%), Oxybenzone (5.4%)</t>
+          <t>Active: Petrolatum 31.0%...Purpose: Skin Protectant, Avobenzone 3.0%...Purpose: Sunscreen, Octinoxate 6.75%...Purpose: Sunscreen, Octisalate 4.5%...Purpose: Sunscreen, Octocrylene 2.0%...Purpose: Sunscreen, Oxybenzone 5.4%...Purpose: Sunscreen. Inactive: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Glycerin, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Panthenol, Water, Polyglyceryl-3 Diisostearate, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, Beeswax, C20-40 Alkyl Stearate, Magnesium Sulfate, Magnesium Stearate, BHT.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1320,15 +1288,19 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Avobenzone [2] / Octinoxate [2] / Octisalate [2] / Octocrylene [2] / Oxybenzone [2]</t>
+          <t>Petrolatum [1] / Avobenzone [2] / Octinoxate [2] / Octisalate [2] / Octocrylene [2] / Oxybenzone [2] / BHT [1,2]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, C20-40 Alkyl Stearate, Magnesium Stearate</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -1336,17 +1308,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Provisional (brand-site partial list only).</t>
+          <t>7 flagged ingredient(s) in the printed list (Petrolatum, Avobenzone, Octinoxate); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Provisional: tier from brand-site partial list only. no retailer INCI found yet. The single Lip Protectant + SPF 30 (0.35 oz tube) matched on Walmart; no Dual Pack listing with matching actives located on Walmart or Target search. Not used.</t>
+          <t>Audit notes: Amazon listing Aquaphor Lip Balm, Lip Repair, SPF 30, 0.35 Oz Tube, Pack of 2 (B0D14XMH8R). Variant match: SPF 30 lip protectant, 2 x 0.35 oz. Actives match brand site text in name and percentage (Petrolatum 31%, Avobenzone 3%, Octinoxate 6.75%, Octisalate 4.5%, Octocrylene 2%, Oxybenzone 5.4%). Verbatim copied with Active and Inactive labels and Purpose tags as printed. Not verified on CVS, Walgreens, Ulta or Dermstore (CVS brand shop showed only a single lip repair plus sunscreen stick; Dermstore does not stock Aquaphor). Walmart pack was not used because it is a single SPF 30 tube. REVIEW: the row keeps product_type sunscreen from the prior pass. The grader escalates a cat. 1 flag to High Priority Swap only for leave-on skincare, so this row grades Avoid (Moderate) with 7 flags. The single Lip Protectant + SPF 30 row (lip product type, 7 flags) grades High Priority Swap. Both are leave-on tubes; Nina to confirm the type. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF 30. Ingredient source: Amazon - https://www.amazon.com/dp/B0D14XMH8R.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1364,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Octyldodecanol, Bis-Diglyceryl Polyacyladipate-2, Tocopheryl Acetate, Ascorbyl Palmitate</t>
+          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Ascorbyl Palmitate, Helianthus Annuus (Sunflower) Seed Oil</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1402,12 +1374,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s): Avobenzone, Homosalate, Octisalate, Octocrylene.... Escalation: PFAS.</t>
+          <t>5 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Protect-SPF-30-Stick-Dual-Pack-0-34oz-Pack-of-2-sticks/15665510241). Brand site showed partial list only: Avobenzone (3%), Homosalate (9%), Octisalate (4.5%), Octocrylene (9%). Walmart listing 'Aquaphor Lip Repair &amp; Protect SPF 30 Stick, 2pk, 0.35oz, Clear'. Cross-check: actives match brand site (Avobenzone 3, Homosalate 9, Octisalate 4.5, Octocrylene 9). Retailer 2-pack title, same product.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair &amp; Protect SPF 30 Stick, 2pk, 0.35oz, Clear'. Cross-check: actives match brand site (Avobenzone 3, Homosalate 9, Octisalate 4.5, Octocrylene 9). Retailer 2-pack title, same product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Protect-SPF-30-Stick-Dual-Pack-0-34oz-Pack-of-2-sticks/15665510241.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1448,21 +1420,17 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1472,12 +1440,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (14oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1514,32 +1482,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Caprylic/Capric Triglyceride, Glycerin, Bis-Diglyceryl Polyacyladipate-2, Water, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Lecithin, Ascorbyl Palmitate, C20-40 Alkyl Stearate, Magnesium Stearate, Glyceryl Stearate</t>
+          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Sodium Ascorbyl Phosphate, Lecithin, Ascorbyl Palmitate, C20-40 Alkyl Stearate, Magnesium Stearate</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the full list per reference.</t>
+          <t>1 flagged ingredient(s) in the printed list (Bisabolol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970). Brand site showed partial list only: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis Seed Oil. Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1590,7 +1558,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Octyldodecanol, Bis-Diglyceryl Polyacyladipate-2, Water, Tocopheryl Acetate, Ascorbyl Palmitate</t>
+          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1600,12 +1568,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s): Dimethicone. Escalation: PFAS.</t>
+          <t>1 flagged ingredient(s) in the printed list (Dimethicone); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/304762780). Brand site showed partial list only: Octyldodecanol, Ricinus Communis Seed Oil, Beeswax. Walmart listing 'Aquaphor, Lip Repair Balm Stick, 0.17 oz, 2 Pack for Dry Chapped Lips'. Cross-check: first three match brand site. Same printed list as the single Lip Repair Stick. Dimethicone appears in retailer list only.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Balm Stick, 0.17 oz, 2 Pack for Dry Chapped Lips'. Cross-check: first three match brand site. Same printed list as the single Lip Repair Stick. Dimethicone appears in retailer list only. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/304762780.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1646,21 +1614,17 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Caprylic/Capric Triglyceride, Glycerin</t>
+          <t>unknown — manual review needed: Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1670,12 +1634,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s): Petrolatum. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860). Brand site showed partial list only: Petrolatum (30%). Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches. Identical printed text on 1 other product(s): Aquaphor® Healing Balm Stick (0.65oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1712,32 +1676,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (Moderate)</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sodium Myreth Sulfate [inferred: sulfate] [1,4,5] / PEG-200 Hydrogenated Glyceryl Palmate [inferred: PEG-] [1,2,4,5] / Cocamidopropyl Betaine [1,4] / Bisabolol [4]</t>
+          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / PEG-200 Hydrogenated Glyceryl Palmate [1,2,4,5] (inferred: PEG-) / Cocamidopropyl Betaine [1,4] / Bisabolol [4] (natural component, no source essential oil listed: full flag) / Polyquaternium-10 [2] (inferred: -nium quat)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Water, Polyquaternium-10, Sea Salt</t>
+          <t>unknown — manual review needed: Sea Salt</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s): Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine, Bisabolol.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-and-Shampoo-Unscented-Baby-Shampoo-and-Wash-25-4-Fl-Oz-Pump-Bottle/5032877839). Brand site showed partial list only: Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate. Walmart listing 'Aquaphor Baby Wash &amp; Shampoo, Fragrance Free and Tear Free, 25.4 fl oz'. Cross-check: first three (Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate) match brand site. Panel text was read from the listing's collapsible Ingredients block; ancestry check was inconclusive, so re-verify this row if Nina wants a second look. Sodium Myreth Sulfate is a sulfate and is flagged by the grader.</t>
+          <t>Audit notes: Second-look verification. Amazon listing (B01NAFQIJ9, titled Aquaphor Baby Body Wash and Shampoo, 25.4 FL OZ, Fragrance Free, Tear Free) Ingredients block matches the user-supplied list word for word. CONFLICT with brand site text: brand text is Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate; Amazon/user list has Sodium Myreth Sulfate in position 3 and PEG-200 Hydrogenated Glyceryl Palmate in position 4. Both texts kept (brand_site_text unchanged). Earlier Walmart attribution for this row was not confirmed and has been replaced. Sodium Myreth Sulfate is a sulfate and is flagged by the grader. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (16.9 fl.oz). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). Ingredient source: Amazon (user-supplied, confirmed on listing) - https://www.amazon.com/dp/B01NAFQIJ9.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1782,13 +1746,13 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Ethylhexylglycerin [4,5]</t>
+          <t>Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / Ethylhexylglycerin [4,5]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Ceramide NP, Glycine Soja (Soybean) Oil</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1798,12 +1762,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s): Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Lotion-3oz/19974261109). Brand site showed partial list only: Water, Glycerin, Cetearyl Alcohol. Walmart listing 'Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 fl oz'. Cross-check: first three match brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 fl oz'. Cross-check: first three match brand site. Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 8 Fl Oz. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Lotion-3oz/19974261109.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1848,13 +1812,13 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [inferred: sulfate] [1,4,5] / Ethylhexylglycerin [4,5]</t>
+          <t>Phenoxyethanol [1,2,4,5,8] / Sodium Cetearyl Sulfate [1,4,5] (inferred: sulfate) / Ethylhexylglycerin [4,5]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Ceramide NP, Glycine Soja (Soybean) Oil</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1864,12 +1828,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s): Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Daily-Lotion-8-oz/19736656895). Brand site showed partial list only: Water, Glycerin, Cetearyl Alcohol. Walmart listing 'Aquaphor, Baby Sensitive Lotion, Baby Lotion, 8 fl oz'. Cross-check: first three match brand site (Water, Glycerin, Cetearyl Alcohol).</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Sensitive Lotion, Baby Lotion, 8 fl oz'. Cross-check: first three match brand site (Water, Glycerin, Cetearyl Alcohol). Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 Fl Oz. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Daily-Lotion-8-oz/19736656895.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1910,21 +1874,17 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1934,12 +1894,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1980,21 +1940,17 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2004,12 +1960,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (7oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2039,36 +1995,26 @@
           <t>leave-on skincare</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Zinc Oxide (15%)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Puberty Safe</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Provisional (brand-site partial list only).</t>
+          <t>Not graded: no ingredient text on the source page.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Provisional: tier from brand-site partial list only. variant mismatch. Walmart Aquaphor Diaper Rash Cream listings are 3.5 oz only. The brand list says 3 oz. Not used.</t>
+          <t>UNRESOLVED. Size mismatch. Brand row is 3 oz. Retailers checked: CVS (Aquaphor Baby Diaper Rash Paste 3.5 oz only, not a cream match); Walgreens (Aquaphor Baby Diaper Rash Cream with Zinc Oxide 3.5 oz, not a 3 oz match); Amazon (Baby Diaper Rash Cream with Zinc Oxide Multipack 3 x 3.5 oz and Diaper Rash Paste 3.5 oz, not a 3 oz match); Dermstore (no Aquaphor brand); Walmart (3.5 oz only per earlier pass). Ulta blocked. Brand text Zinc Oxide (15%) kept for reference. No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>ingredients not found</t>
         </is>
       </c>
     </row>
@@ -2108,13 +2054,13 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Avobenzone [2] / Octinoxate [2] / Octisalate [2] / Octocrylene [2] / Oxybenzone [2] / BHT [inferred: BHT] [1,2]</t>
+          <t>Petrolatum [1] / Avobenzone [2] / Octinoxate [2] / Octisalate [2] / Octocrylene [2] / Oxybenzone [2] / BHT [1,2]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Glycerin, Caprylic/Capric Triglyceride, Water, Tocopheryl Acetate, C20-40 Alkyl Stearate, Magnesium Stearate</t>
+          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, C20-40 Alkyl Stearate, Magnesium Stearate</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2124,12 +2070,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s): Petrolatum, Avobenzone, Octinoxate, Octisalate.... Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Petrolatum, Avobenzone, Octinoxate); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Lip-Balm-with-Sunscreen-Lip-Balm-SPF-30-0-35-Oz-Tube/23623346). Brand site showed partial list only: Petrolatum (31%), Avobenzone (3%), Octinoxate (6.75%), Octisalate (4.5%), Octocrylene (2%), Oxybenzone (5.4%). Walmart listing 'Aquaphor, Lip Repair Lip Balm with Sunscreen, SPF 30, 0.35 fl oz' (tube). Cross-check: all six actives match brand-site values exactly.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Lip Balm with Sunscreen, SPF 30, 0.35 fl oz' (tube). Cross-check: all six actives match brand-site values exactly. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF (Dual Pack). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Lip-Balm-with-Sunscreen-Lip-Balm-SPF-30-0-35-Oz-Tube/23623346.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2166,32 +2112,32 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Caprylic/Capric Triglyceride, Glycerin, Bis-Diglyceryl Polyacyladipate-2, Water, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, C20-40 Alkyl Stearate, Magnesium Stearate</t>
+          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Sodium Ascorbyl Phosphate, C20-40 Alkyl Stearate, Magnesium Stearate</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the full list per reference.</t>
+          <t>1 flagged ingredient(s) in the printed list (Bisabolol); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721). Brand site showed partial list only: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis Seed Oil. Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2232,21 +2178,17 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2256,12 +2198,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2302,21 +2244,17 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2326,12 +2264,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2368,32 +2306,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avoid (Mild)</t>
+          <t>Avoid (Moderate)</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sodium Myreth Sulfate [inferred: sulfate] [1,4,5] / PEG-200 Hydrogenated Glyceryl Palmate [inferred: PEG-] [1,2,4,5] / Cocamidopropyl Betaine [1,4] / Bisabolol [4]</t>
+          <t>Sodium Myreth Sulfate [1,4,5] (inferred: sulfate) / PEG-200 Hydrogenated Glyceryl Palmate [1,2,4,5] (inferred: PEG-) / Cocamidopropyl Betaine [1,4] / Bisabolol [4] (natural component, no source essential oil listed: full flag) / Polyquaternium-10 [2] (inferred: -nium quat)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Water, Polyquaternium-10, Sea Salt</t>
+          <t>unknown — manual review needed: Sea Salt</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s): Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine, Bisabolol.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301). Brand site showed partial list only: Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate. Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (25.4oz.). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2434,21 +2372,17 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Butane, Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Butane, Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2458,12 +2392,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182). Brand site showed partial list only: Butane, Petrolatum, Mineral Oil. Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2504,21 +2438,17 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2528,12 +2458,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2574,21 +2504,17 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2598,12 +2524,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2644,21 +2570,17 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Hydrocortisone, Ceresin, Lanolin Alcohol, Glycerin, Menthoxypropanediol</t>
+          <t>unknown — manual review needed: Hydrocortisone, Ceresin, Lanolin Alcohol, Menthoxypropanediol</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2668,12 +2590,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819). Brand site showed partial list only: Hydrocortisone (1%). Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2705,7 +2627,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Petrolatum (30%)</t>
+          <t>Active ingredients: Petrolatum 30% (Purpose: Skin Protectant)... Inactive ingredients: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Beeswax, Butyrospermum Parkii (Shea) Butter, Tocopherol, Panthenol, Glycerin, Bisabolol.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2714,15 +2636,19 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Petrolatum [1]</t>
+          <t>Petrolatum [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>unknown — manual review needed: Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>carcinogen in leave-on</t>
@@ -2730,17 +2656,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Provisional (brand-site partial list only).</t>
+          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Provisional: tier from brand-site partial list only. no retailer INCI found on Walmart. The Aquaphor Healing Balm Stick 0.65 oz (Pack of 3) listing shows no Ingredients block. Retry elsewhere.</t>
+          <t>Audit notes: Walmart listing (3 pack) Aquaphor Healing Balm Stick, 0.65 oz (listing 15374315224). Ingredients block sat under a collapsed section; expanded and read. Variant match: 3-pack. Cross-check: brand site text Petrolatum (30%) matches the active. Verbatim keeps the Active/Inactive label and the Purpose tag as printed. Other listings checked before this one: Walmart 0.65 oz Pack of 3 (7455005955), which the earlier pass reported with no ingredients block; not re-checked. Note: the Walmart listing is a 3-pack, and the Amazon and Walgreens listings found are single 0.65 oz sticks, not used. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Balm Stick (0.65oz.). Ingredient source: Walmart (3 pack) - https://www.walmart.com/ip/3-pack-Aquaphor-Healing-Balm-Stick-Skin-Protectant-0-65-Oz-Stick/15374315224.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2765,40 +2691,26 @@
           <t>leave-on skincare</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Water, Glycerin, Urea</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Puberty Safe</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Water, Glycerin, Urea</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Provisional (brand-site partial list only).</t>
+          <t>Not graded: no ingredient text on the source page.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Provisional: tier from brand-site partial list only. no retailer INCI found. Walmart (1-pair hand mask) and Target (Advanced Therapy Repairing Hand Mask 0.7 fl oz) listings show no printed Ingredients block for the product. Not used.</t>
+          <t>UNRESOLVED. Retailers checked: CVS (no Hand Mask result; brand shop lists Foot Masks only); Walgreens (no Hand Mask result); Ulta (blocked, Be Right Back page, could not load); Dermstore (no Aquaphor brand stocked); Amazon (only Advanced Therapy Repairing Hand Masks, 6 Masks x 0.7 FL OZ, B0B5FJFWW8, a 6-pack, not a single-unit match, not used); Target (A-86416643, Repairing Hand Mask 0.7 fl oz; Ingredients and Label info panels show no readable text, not used); Walmart (1791022082, Repairing Hand Masks 1 Pair; no readable Ingredients text after expanding, not used). Brand text Water, Glycerin, Urea is kept for reference. No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>ingredients not found</t>
         </is>
       </c>
     </row>
@@ -2825,38 +2737,46 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Urea</t>
+          <t>Water, Glycerin, Urea, Hydrogenated Polyisobutene, Dimethicone, Cetearyl Alcohol, Glyceryl Stearate, Butyrospermum Parkii (Shea) Butter, Persea Gratissima (Avocado) Oil, Panthenol, Bisabolol, Tocopheryl Acetate, PEG-100 Stearate, Caprylic/Capric Triglyceride, Betaine, Ceteareth-25, Glyceryl Caprylate, Phenoxyethanol, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Xanthan Gum, Sodium Hydroxide, Disodium EDTA, Hydroxyacetophenone.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Dimethicone [2,6] / Bisabolol [4] (natural component, no source essential oil listed: full flag) / PEG-100 Stearate [1,2,4,5] (inferred: PEG-) / Ceteareth-25 [1,4,5] (inferred: -eth ethoxylate) / Phenoxyethanol [1,2,4,5,8]</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Water, Glycerin, Urea</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>unknown — manual review needed: Hydrogenated Polyisobutene, Butyrospermum Parkii (Shea) Butter, Persea Gratissima (Avocado) Oil, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Hydroxyacetophenone</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>PFAS, carcinogen in leave-on</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Provisional (brand-site partial list only).</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Bisabolol, PEG-100 Stearate); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Provisional: tier from brand-site partial list only. no retailer INCI found. Walmart (1-pair foot mask) listing has no printed Aquaphor Ingredients block. Target listing for Advanced Therapy Repairing Foot Mask 0.7 fl oz exists but its ingredients were not visible. Not used.</t>
+          <t>Audit notes: CVS listing Aquaphor Advanced Therapy Repairing Foot Masks, 1 Pair (prodid 648998). CVS shows the full list under Active Ingredients (uppercase) and Inactive Ingredients (title case); both contain the same 24 items in the same order. Title-case Inactive list used verbatim. Cross-check: first three (Water, Glycerin, Urea) match brand site. Target listing (0.7 fl oz) was not used; CVS 1-pair listing taken as the match for the brand row. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-advanced-therapy-repairing-foot-masks-1-pair-prodid-648998.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2892,21 +2812,17 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2916,12 +2832,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2953,7 +2869,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Butane, Petrolatum, Mineral Oil</t>
+          <t>Butane, Petrolatum, Mineral Oil, Ceresin, Lanolin Alcohol, Panthenol, Glycerin, Bisabolol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2962,17 +2878,17 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Butane</t>
+          <t>unknown — manual review needed: Butane, Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2982,17 +2898,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Provisional (brand-site partial list only).</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Provisional: tier from brand-site partial list only. variant mismatch / no retailer INCI found. Walmart lists the Aquaphor Ointment Body Spray in 3.7 oz and multipacks only. The 3.7 oz row is used for the 3.7 oz product; 6.2 oz not located.</t>
+          <t>Audit notes: Amazon listing Aquaphor Advanced Therapy Ointment Body Spray, 6.2 OZ, Pack of 1 (B07TR75W9H). Variant match on size 6.2 oz. Cross-check: first three (Butane, Petrolatum, Mineral Oil) match brand site. CVS (3.7 oz) and Walmart (3.7 oz) listings were not used as they are a different size. Ingredient source: Amazon - https://www.amazon.com/dp/B07TR75W9H.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3028,21 +2944,17 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3052,12 +2964,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor® Children's Healing Ointment (14oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3087,44 +2999,26 @@
           <t>leave-on skincare</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Petrolatum (41%)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Avoid (High Priority Swap)</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Petrolatum [1]</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>carcinogen in leave-on</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Provisional (brand-site partial list only).</t>
+          <t>Not graded: no ingredient text on the source page.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Provisional: tier from brand-site partial list only. variant mismatch / no retailer INCI found. Walmart search for a 2 x 3.5 oz Aquaphor Healing Ointment returned only Baby Diaper Rash Paste 3.5 oz 2-pack and 1.75 oz travel packs. Not used.</t>
+          <t>UNRESOLVED. No 2 x 3.5 oz listing found. Retailers checked: CVS (0.35 oz 2 CT, 1.75 oz, 3 oz No Touch, 5 oz, 7 oz; no 2 x 3.5 oz); Walgreens (0.35 oz x 2 pack, 1.75 oz, 7 oz, 14 oz; no 2 x 3.5 oz); Amazon (Multipack 3 x 2.8 oz, 3 x 1.75 oz, Value Pack 2 x 0.35 oz; no 2 x 3.5 oz); Walmart (0.35 oz x 2, 1.75 oz, 3 x 1.75 oz, 3 x 7 oz; no 2 x 3.5 oz); Target (1.75 oz, 2.8 oz jar; no 2 x 3.5 oz); Dermstore (no Aquaphor brand); Ulta blocked. Brand text Petrolatum (41%) kept for reference. No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>ingredients not found</t>
         </is>
       </c>
     </row>
@@ -3160,21 +3054,17 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Petrolatum [1] / Mineral Oil [1]</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Bisabolol [4,8]</t>
-        </is>
-      </c>
+          <t>Petrolatum [1] / Mineral Oil [1] / Bisabolol [4] (natural component, no source essential oil listed: full flag)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3184,12 +3074,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s): Petrolatum, Mineral Oil. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Full INCI from retailer (Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609). Brand site showed partial list only: Petrolatum (41%). Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Ointment (14oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">

--- a/audits/aquaphor/aquaphor_audit.xlsx
+++ b/audits/aquaphor/aquaphor_audit.xlsx
@@ -530,7 +530,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Tapioca Starch, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan</t>
+          <t>unknown — manual review needed: Water, Glycerin, Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -540,12 +540,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Pentylene Glycol, Sodium Cetearyl Sulfate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Pentylene Glycol, Sodium Cetearyl Sulfate); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'. Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (16oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'. Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (16oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -596,7 +596,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
+          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -662,7 +662,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
+          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -728,7 +728,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
+          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Moisturizing Cream (1.89oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Moisturizing Cream (1.89oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -794,7 +794,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
+          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Audit notes: CONFLICT: CVS ingredients page (Aquaphor Moisturizing Cream, 1.89 OZ, prodid 923320) lists Water, Glycerin, Cetearyl Alcohol as the first three; brand site text lists Water, Glycerin, Caprylic/Capric Triglyceride. Both texts kept (brand_site_text unchanged). Grading uses the CVS verbatim list. Variant matches on name and size. Note the brand text may refer to a different formula or size. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.). Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-moisturizing-cream-1-89-oz-prodid-923320.</t>
+          <t>Audit notes: CONFLICT: CVS ingredients page (Aquaphor Moisturizing Cream, 1.89 OZ, prodid 923320) lists Water, Glycerin, Cetearyl Alcohol as the first three; brand site text lists Water, Glycerin, Caprylic/Capric Triglyceride. Both texts kept (brand_site_text unchanged). Grading uses the CVS verbatim list. Variant matches on name and size. Note the brand text may refer to a different formula or size. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-moisturizing-cream-1-89-oz-prodid-923320.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -860,7 +860,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Tapioca Starch, Ceramide AP, Ceramide NP, Ceramide NG, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan</t>
+          <t>unknown — manual review needed: Water, Glycerin, Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Pentylene Glycol, Sodium Cetearyl Sulfate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Pentylene Glycol, Sodium Cetearyl Sulfate); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride). Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (8oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride). Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (8oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -922,13 +922,13 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Aloe Barbadensis Leaf Juice Powder, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone</t>
+          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Glycerin, Hydrogenated Castor Oil, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Aloe Barbadensis Leaf Juice Powder, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Water, Pantolactone</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 9 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 13 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -980,13 +980,13 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Cocos Nucifera (Coconut) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone</t>
+          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Water, Pantolactone</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 8 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 10 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1042,7 +1042,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin alcohol</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069.</t>
+          <t>Audit notes: Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1104,13 +1104,13 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Butyrospermum Parkii (Shea) Butter</t>
+          <t>unknown — manual review needed: Glycerin, Caprylic/Capric Triglyceride, Octyldodecanol, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Butyrospermum Parkii (Shea) Butter, Water</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 3 unknown ingredient(s) not in reference.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 7 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1166,7 +1166,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate</t>
+          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Water, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Dimethicone); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
+          <t>1 flagged ingredient(s) in the printed list (Dimethicone); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Ascorbyl Palmitate, helianthus annuus (sunflower) seed oil</t>
+          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, helianthus annuus (sunflower) seed oil</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
+          <t>5 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1298,7 +1298,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, C20-40 Alkyl Stearate, Magnesium Stearate</t>
+          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Glycerin, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Water, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Petrolatum, Avobenzone, Octinoxate); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Petrolatum, Avobenzone, Octinoxate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1364,7 +1364,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Ascorbyl Palmitate, Helianthus Annuus (Sunflower) Seed Oil</t>
+          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, Helianthus Annuus (Sunflower) Seed Oil</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
+          <t>5 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1430,7 +1430,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (14oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (14oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1496,18 +1496,18 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Sodium Ascorbyl Phosphate, Lecithin, Ascorbyl Palmitate, C20-40 Alkyl Stearate, Magnesium Stearate</t>
+          <t>unknown — manual review needed: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Glycerin, Bis-Diglyceryl Polyacyladipate-2, Water, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Lecithin, Ascorbyl Palmitate, C20-40 Alkyl Stearate, Magnesium Stearate, Glyceryl Stearate</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Bisabolol); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference.</t>
+          <t>1 flagged ingredient(s) in the printed list (Bisabolol); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1558,7 +1558,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate</t>
+          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Water, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Dimethicone); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
+          <t>1 flagged ingredient(s) in the printed list (Dimethicone); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1624,7 +1624,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter</t>
+          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter, Glycerin</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1634,12 +1634,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Bisabolol); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches. Identical printed text on 1 other product(s): Aquaphor® Healing Balm Stick (0.65oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches. Identical printed text on 1 other product(s): Aquaphor® Healing Balm Stick (0.65oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1690,18 +1690,18 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Sea Salt</t>
+          <t>unknown — manual review needed: Water, Sea Salt</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Audit notes: Second-look verification. Amazon listing (B01NAFQIJ9, titled Aquaphor Baby Body Wash and Shampoo, 25.4 FL OZ, Fragrance Free, Tear Free) Ingredients block matches the user-supplied list word for word. CONFLICT with brand site text: brand text is Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate; Amazon/user list has Sodium Myreth Sulfate in position 3 and PEG-200 Hydrogenated Glyceryl Palmate in position 4. Both texts kept (brand_site_text unchanged). Earlier Walmart attribution for this row was not confirmed and has been replaced. Sodium Myreth Sulfate is a sulfate and is flagged by the grader. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (16.9 fl.oz). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). Ingredient source: Amazon (user-supplied, confirmed on listing) - https://www.amazon.com/dp/B01NAFQIJ9.</t>
+          <t>Audit notes: Second-look verification. Amazon listing (B01NAFQIJ9, titled Aquaphor Baby Body Wash and Shampoo, 25.4 FL OZ, Fragrance Free, Tear Free) Ingredients block matches the user-supplied list word for word. CONFLICT with brand site text: brand text is Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate; Amazon/user list has Sodium Myreth Sulfate in position 3 and PEG-200 Hydrogenated Glyceryl Palmate in position 4. Both texts kept (brand_site_text unchanged). Earlier Walmart attribution for this row was not confirmed and has been replaced. Sodium Myreth Sulfate is a sulfate and is flagged by the grader. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (16.9 fl.oz). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon (user-supplied, confirmed on listing) - https://www.amazon.com/dp/B01NAFQIJ9.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1752,7 +1752,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Ceramide NP, Glycine Soja (Soybean) Oil</t>
+          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1818,7 +1818,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ethylhexyl Stearate, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Ceramide NP, Glycine Soja (Soybean) Oil</t>
+          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1884,7 +1884,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1894,12 +1894,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1950,7 +1950,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (7oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (7oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2060,7 +2060,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, C20-40 Alkyl Stearate, Magnesium Stearate</t>
+          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Glycerin, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Water, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Petrolatum, Avobenzone, Octinoxate); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Petrolatum, Avobenzone, Octinoxate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2126,18 +2126,18 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Sodium Ascorbyl Phosphate, C20-40 Alkyl Stearate, Magnesium Stearate</t>
+          <t>unknown — manual review needed: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Glycerin, Bis-Diglyceryl Polyacyladipate-2, Water, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, C20-40 Alkyl Stearate, Magnesium Stearate</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Bisabolol); tier applies to the printed subset only. 7 unknown ingredient(s) not in reference.</t>
+          <t>1 flagged ingredient(s) in the printed list (Bisabolol); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2188,7 +2188,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2254,7 +2254,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2320,18 +2320,18 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Sea Salt</t>
+          <t>unknown — manual review needed: Water, Sea Salt</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (25.4oz.). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (25.4oz.). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2382,7 +2382,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Butane, Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Butane, Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2448,7 +2448,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2514,7 +2514,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2580,7 +2580,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Hydrocortisone, Ceresin, Lanolin Alcohol, Menthoxypropanediol</t>
+          <t>unknown — manual review needed: Hydrocortisone, Ceresin, Lanolin Alcohol, Glycerin, Menthoxypropanediol</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2646,7 +2646,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter</t>
+          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter, Glycerin</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Bisabolol); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing (3 pack) Aquaphor Healing Balm Stick, 0.65 oz (listing 15374315224). Ingredients block sat under a collapsed section; expanded and read. Variant match: 3-pack. Cross-check: brand site text Petrolatum (30%) matches the active. Verbatim keeps the Active/Inactive label and the Purpose tag as printed. Other listings checked before this one: Walmart 0.65 oz Pack of 3 (7455005955), which the earlier pass reported with no ingredients block; not re-checked. Note: the Walmart listing is a 3-pack, and the Amazon and Walgreens listings found are single 0.65 oz sticks, not used. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Balm Stick (0.65oz.). Ingredient source: Walmart (3 pack) - https://www.walmart.com/ip/3-pack-Aquaphor-Healing-Balm-Stick-Skin-Protectant-0-65-Oz-Stick/15374315224.</t>
+          <t>Audit notes: Walmart listing (3 pack) Aquaphor Healing Balm Stick, 0.65 oz (listing 15374315224). Ingredients block sat under a collapsed section; expanded and read. Variant match: 3-pack. Cross-check: brand site text Petrolatum (30%) matches the active. Verbatim keeps the Active/Inactive label and the Purpose tag as printed. Other listings checked before this one: Walmart 0.65 oz Pack of 3 (7455005955), which the earlier pass reported with no ingredients block; not re-checked. Note: the Walmart listing is a 3-pack, and the Amazon and Walgreens listings found are single 0.65 oz sticks, not used. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Balm Stick (0.65oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart (3 pack) - https://www.walmart.com/ip/3-pack-Aquaphor-Healing-Balm-Stick-Skin-Protectant-0-65-Oz-Stick/15374315224.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2756,7 +2756,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Hydrogenated Polyisobutene, Butyrospermum Parkii (Shea) Butter, Persea Gratissima (Avocado) Oil, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Disodium EDTA, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: Water, Glycerin, Urea, Hydrogenated Polyisobutene, Glyceryl Stearate, Butyrospermum Parkii (Shea) Butter, Persea Gratissima (Avocado) Oil, Tocopheryl Acetate, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Disodium EDTA, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2766,12 +2766,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Bisabolol, PEG-100 Stearate); tier applies to the printed subset only. 6 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Bisabolol, PEG-100 Stearate); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Audit notes: CVS listing Aquaphor Advanced Therapy Repairing Foot Masks, 1 Pair (prodid 648998). CVS shows the full list under Active Ingredients (uppercase) and Inactive Ingredients (title case); both contain the same 24 items in the same order. Title-case Inactive list used verbatim. Cross-check: first three (Water, Glycerin, Urea) match brand site. Target listing (0.7 fl oz) was not used; CVS 1-pair listing taken as the match for the brand row. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-advanced-therapy-repairing-foot-masks-1-pair-prodid-648998.</t>
+          <t>Audit notes: CVS listing Aquaphor Advanced Therapy Repairing Foot Masks, 1 Pair (prodid 648998). CVS shows the full list under Active Ingredients (uppercase) and Inactive Ingredients (title case); both contain the same 24 items in the same order. Title-case Inactive list used verbatim. Cross-check: first three (Water, Glycerin, Urea) match brand site. Target listing (0.7 fl oz) was not used; CVS 1-pair listing taken as the match for the brand row. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-advanced-therapy-repairing-foot-masks-1-pair-prodid-648998.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2822,7 +2822,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2888,7 +2888,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Butane, Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Butane, Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Audit notes: Amazon listing Aquaphor Advanced Therapy Ointment Body Spray, 6.2 OZ, Pack of 1 (B07TR75W9H). Variant match on size 6.2 oz. Cross-check: first three (Butane, Petrolatum, Mineral Oil) match brand site. CVS (3.7 oz) and Walmart (3.7 oz) listings were not used as they are a different size. Ingredient source: Amazon - https://www.amazon.com/dp/B07TR75W9H.</t>
+          <t>Audit notes: Amazon listing Aquaphor Advanced Therapy Ointment Body Spray, 6.2 OZ, Pack of 1 (B07TR75W9H). Variant match on size 6.2 oz. Cross-check: first three (Butane, Petrolatum, Mineral Oil) match brand site. CVS (3.7 oz) and Walmart (3.7 oz) listings were not used as they are a different size. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon - https://www.amazon.com/dp/B07TR75W9H.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2954,7 +2954,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor® Children's Healing Ointment (14oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor® Children's Healing Ointment (14oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3064,7 +3064,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Ointment (14oz.). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Ointment (14oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">

--- a/audits/aquaphor/aquaphor_audit.xlsx
+++ b/audits/aquaphor/aquaphor_audit.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -530,7 +530,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil</t>
+          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -540,17 +540,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Pentylene Glycol, Sodium Cetearyl Sulfate); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'. Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (16oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'. Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -596,7 +596,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -606,17 +606,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -662,7 +662,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -728,7 +728,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -738,17 +738,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Moisturizing Cream (1.89oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -794,7 +794,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -804,17 +804,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Audit notes: CONFLICT: CVS ingredients page (Aquaphor Moisturizing Cream, 1.89 OZ, prodid 923320) lists Water, Glycerin, Cetearyl Alcohol as the first three; brand site text lists Water, Glycerin, Caprylic/Capric Triglyceride. Both texts kept (brand_site_text unchanged). Grading uses the CVS verbatim list. Variant matches on name and size. Note the brand text may refer to a different formula or size. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-moisturizing-cream-1-89-oz-prodid-923320.</t>
+          <t>Audit notes: CONFLICT: CVS ingredients page (Aquaphor Moisturizing Cream, 1.89 OZ, prodid 923320) lists Water, Glycerin, Cetearyl Alcohol as the first three; brand site text lists Water, Glycerin, Caprylic/Capric Triglyceride. Both texts kept (brand_site_text unchanged). Grading uses the CVS verbatim list. Variant matches on name and size. Note the brand text may refer to a different formula or size. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-moisturizing-cream-1-89-oz-prodid-923320.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -860,7 +860,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil</t>
+          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -870,17 +870,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Pentylene Glycol, Sodium Cetearyl Sulfate); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride). Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (8oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride). Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (8oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -922,23 +922,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Glycerin, Hydrogenated Castor Oil, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Aloe Barbadensis Leaf Juice Powder, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Water, Pantolactone</t>
+          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Aloe Barbadensis Leaf Juice Powder, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 13 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Aloe Vera, 0.17 oz' (single stick). Cross-check: first three match brand site. Brand-site list named Ricinus Communis Seed Oil; retailer uses Ricinus Communis (Castor) Seed Oil, same ingredient. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Aloe-Vera-0-17-oz-Stick/5322031840.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Aloe Vera, 0.17 oz' (single stick). Cross-check: first three match brand site. Brand-site list named Ricinus Communis Seed Oil; retailer uses Ricinus Communis (Castor) Seed Oil, same ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Aloe Barbadensis Leaf Juice Powder, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Aloe-Vera-0-17-oz-Stick/5322031840.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -980,23 +980,23 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Water, Pantolactone</t>
+          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 10 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Coconut Oil, 0.17 oz' (single stick). Cross-check: first three match brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Coconut-Oil-0-17-oz-Stick/5415018384.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Coconut Oil, 0.17 oz' (single stick). Cross-check: first three match brand site. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Coconut-Oil-0-17-oz-Stick/5415018384.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1042,7 +1042,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin alcohol</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1052,17 +1052,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069.</t>
+          <t>Audit notes: Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1104,23 +1104,23 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Glycerin, Caprylic/Capric Triglyceride, Octyldodecanol, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Butyrospermum Parkii (Shea) Butter, Water</t>
+          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Octyldodecanol, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Butyrospermum Parkii (Shea) Butter</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 7 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 5 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Diaper Rash Paste, Maximum Strength 40% Zinc Oxide, 3.5 oz'. Cross-check: brand-site Zinc Oxide (40%) matches the active. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Diaper-Rash-Paste-Maximum-Strength-40-Zinc-Oxide-Diaper-Rash-Cream-Diaper-Rash-Ointment-3-5-oz/299965693.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Diaper Rash Paste, Maximum Strength 40% Zinc Oxide, 3.5 oz'. Cross-check: brand-site Zinc Oxide (40%) matches the active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Octyldodecanol, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Butyrospermum Parkii (Shea) Butter. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Diaper-Rash-Paste-Maximum-Strength-40-Zinc-Oxide-Diaper-Rash-Cream-Diaper-Rash-Ointment-3-5-oz/299965693.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1166,7 +1166,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Water, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate</t>
+          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Dimethicone); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
+          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Balm Stick for Dry Chapped Lips with Shea Butter, 0.17 oz'. Cross-check: first three match brand site. Dimethicone appears in this retailer list but not in the brand-site partial list; flagged for grader. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick (Dual Pack). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/621710698.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Balm Stick for Dry Chapped Lips with Shea Butter, 0.17 oz'. Cross-check: first three match brand site. Dimethicone appears in this retailer list but not in the brand-site partial list; flagged for grader. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick (Dual Pack). D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/621710698.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Broad Spectrum SPF 30 Lip Repair Stick + Sunscreen 0.17 oz'. Cross-check: actives Avobenzone, Homosalate, Octisalate, Octocrylene match brand site. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Spf-30/1370153078.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Broad Spectrum SPF 30 Lip Repair Stick + Sunscreen 0.17 oz'. Cross-check: actives Avobenzone, Homosalate, Octisalate, Octocrylene match brand site. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, helianthus annuus (sunflower) seed oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Spf-30/1370153078.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1298,7 +1298,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Glycerin, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Water, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate</t>
+          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Petrolatum, Avobenzone, Octinoxate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Audit notes: Amazon listing Aquaphor Lip Balm, Lip Repair, SPF 30, 0.35 Oz Tube, Pack of 2 (B0D14XMH8R). Variant match: SPF 30 lip protectant, 2 x 0.35 oz. Actives match brand site text in name and percentage (Petrolatum 31%, Avobenzone 3%, Octinoxate 6.75%, Octisalate 4.5%, Octocrylene 2%, Oxybenzone 5.4%). Verbatim copied with Active and Inactive labels and Purpose tags as printed. Not verified on CVS, Walgreens, Ulta or Dermstore (CVS brand shop showed only a single lip repair plus sunscreen stick; Dermstore does not stock Aquaphor). Walmart pack was not used because it is a single SPF 30 tube. REVIEW: the row keeps product_type sunscreen from the prior pass. The grader escalates a cat. 1 flag to High Priority Swap only for leave-on skincare, so this row grades Avoid (Moderate) with 7 flags. The single Lip Protectant + SPF 30 row (lip product type, 7 flags) grades High Priority Swap. Both are leave-on tubes; Nina to confirm the type. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF 30. Ingredient source: Amazon - https://www.amazon.com/dp/B0D14XMH8R.</t>
+          <t>Audit notes: Amazon listing Aquaphor Lip Balm, Lip Repair, SPF 30, 0.35 Oz Tube, Pack of 2 (B0D14XMH8R). Variant match: SPF 30 lip protectant, 2 x 0.35 oz. Actives match brand site text in name and percentage (Petrolatum 31%, Avobenzone 3%, Octinoxate 6.75%, Octisalate 4.5%, Octocrylene 2%, Oxybenzone 5.4%). Verbatim copied with Active and Inactive labels and Purpose tags as printed. Not verified on CVS, Walgreens, Ulta or Dermstore (CVS brand shop showed only a single lip repair plus sunscreen stick; Dermstore does not stock Aquaphor). Walmart pack was not used because it is a single SPF 30 tube. REVIEW: the row keeps product_type sunscreen from the prior pass. The grader escalates a cat. 1 flag to High Priority Swap only for leave-on skincare, so this row grades Avoid (Moderate) with 7 flags. The single Lip Protectant + SPF 30 row (lip product type, 7 flags) grades High Priority Swap. Both are leave-on tubes; Nina to confirm the type. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF 30. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate. Ingredient source: Amazon - https://www.amazon.com/dp/B0D14XMH8R.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair &amp; Protect SPF 30 Stick, 2pk, 0.35oz, Clear'. Cross-check: actives match brand site (Avobenzone 3, Homosalate 9, Octisalate 4.5, Octocrylene 9). Retailer 2-pack title, same product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Protect-SPF-30-Stick-Dual-Pack-0-34oz-Pack-of-2-sticks/15665510241.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair &amp; Protect SPF 30 Stick, 2pk, 0.35oz, Clear'. Cross-check: actives match brand site (Avobenzone 3, Homosalate 9, Octisalate 4.5, Octocrylene 9). Retailer 2-pack title, same product. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Protect-SPF-30-Stick-Dual-Pack-0-34oz-Pack-of-2-sticks/15665510241.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1430,7 +1430,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1440,17 +1440,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (14oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1496,23 +1496,23 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Glycerin, Bis-Diglyceryl Polyacyladipate-2, Water, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Lecithin, Ascorbyl Palmitate, C20-40 Alkyl Stearate, Magnesium Stearate, Glyceryl Stearate</t>
+          <t>unknown — manual review needed: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Lecithin, Ascorbyl Palmitate, C20-40 Alkyl Stearate, Magnesium Stearate, Glyceryl Stearate</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Bisabolol); tier applies to the printed subset only. 16 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Lecithin, Ascorbyl Palmitate, C20-40 Alkyl Stearate, Magnesium Stearate, Glyceryl Stearate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1558,7 +1558,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Water, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate</t>
+          <t>unknown — manual review needed: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1568,17 +1568,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Dimethicone); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: PFAS.</t>
+          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Balm Stick, 0.17 oz, 2 Pack for Dry Chapped Lips'. Cross-check: first three match brand site. Same printed list as the single Lip Repair Stick. Dimethicone appears in retailer list only. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/304762780.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Balm Stick, 0.17 oz, 2 Pack for Dry Chapped Lips'. Cross-check: first three match brand site. Same printed list as the single Lip Repair Stick. Dimethicone appears in retailer list only. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/304762780.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1624,7 +1624,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter, Glycerin</t>
+          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1634,17 +1634,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Bisabolol); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 4 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches. Identical printed text on 1 other product(s): Aquaphor® Healing Balm Stick (0.65oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches. Identical printed text on 1 other product(s): Aquaphor® Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avoid (Moderate)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1690,23 +1690,23 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Sea Salt</t>
+          <t>unknown — manual review needed: Sea Salt</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Audit notes: Second-look verification. Amazon listing (B01NAFQIJ9, titled Aquaphor Baby Body Wash and Shampoo, 25.4 FL OZ, Fragrance Free, Tear Free) Ingredients block matches the user-supplied list word for word. CONFLICT with brand site text: brand text is Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate; Amazon/user list has Sodium Myreth Sulfate in position 3 and PEG-200 Hydrogenated Glyceryl Palmate in position 4. Both texts kept (brand_site_text unchanged). Earlier Walmart attribution for this row was not confirmed and has been replaced. Sodium Myreth Sulfate is a sulfate and is flagged by the grader. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (16.9 fl.oz). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon (user-supplied, confirmed on listing) - https://www.amazon.com/dp/B01NAFQIJ9.</t>
+          <t>Audit notes: Second-look verification. Amazon listing (B01NAFQIJ9, titled Aquaphor Baby Body Wash and Shampoo, 25.4 FL OZ, Fragrance Free, Tear Free) Ingredients block matches the user-supplied list word for word. CONFLICT with brand site text: brand text is Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate; Amazon/user list has Sodium Myreth Sulfate in position 3 and PEG-200 Hydrogenated Glyceryl Palmate in position 4. Both texts kept (brand_site_text unchanged). Earlier Walmart attribution for this row was not confirmed and has been replaced. Sodium Myreth Sulfate is a sulfate and is flagged by the grader. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (16.9 fl.oz). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sea Salt. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon (user-supplied, confirmed on listing) - https://www.amazon.com/dp/B01NAFQIJ9.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1752,7 +1752,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1762,17 +1762,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 fl oz'. Cross-check: first three match brand site. Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 8 Fl Oz. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Lotion-3oz/19974261109.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 fl oz'. Cross-check: first three match brand site. Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 8 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Lotion-3oz/19974261109.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1818,7 +1818,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil</t>
+          <t>unknown — manual review needed: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 10 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Sensitive Lotion, Baby Lotion, 8 fl oz'. Cross-check: first three match brand site (Water, Glycerin, Cetearyl Alcohol). Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 Fl Oz. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Daily-Lotion-8-oz/19736656895.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Sensitive Lotion, Baby Lotion, 8 fl oz'. Cross-check: first three match brand site (Water, Glycerin, Cetearyl Alcohol). Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Daily-Lotion-8-oz/19736656895.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1884,7 +1884,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1950,7 +1950,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1960,17 +1960,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (7oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (7oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -1996,20 +1996,26 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ungradable</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Not graded: no ingredient text on the source page.</t>
+          <t>Ungradable: no ingredient text on the source page, so no tier is assigned.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>UNRESOLVED. Size mismatch. Brand row is 3 oz. Retailers checked: CVS (Aquaphor Baby Diaper Rash Paste 3.5 oz only, not a cream match); Walgreens (Aquaphor Baby Diaper Rash Cream with Zinc Oxide 3.5 oz, not a 3 oz match); Amazon (Baby Diaper Rash Cream with Zinc Oxide Multipack 3 x 3.5 oz and Diaper Rash Paste 3.5 oz, not a 3 oz match); Dermstore (no Aquaphor brand); Walmart (3.5 oz only per earlier pass). Ulta blocked. Brand text Zinc Oxide (15%) kept for reference. No verbatim ingredient text in the json; not graded.</t>
+          <t>UNRESOLVED. Size mismatch. Brand row is 3 oz. Retailers checked: CVS (Aquaphor Baby Diaper Rash Paste 3.5 oz only, not a cream match); Walgreens (Aquaphor Baby Diaper Rash Cream with Zinc Oxide 3.5 oz, not a 3 oz match); Amazon (Baby Diaper Rash Cream with Zinc Oxide Multipack 3 x 3.5 oz and Diaper Rash Paste 3.5 oz, not a 3 oz match); Dermstore (no Aquaphor brand); Walmart (3.5 oz only per earlier pass). Ulta blocked. Brand text Zinc Oxide (15%) kept for reference. No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2046,7 +2052,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2060,7 +2066,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Glycerin, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Water, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate</t>
+          <t>unknown — manual review needed: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2070,17 +2076,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>7 flagged ingredient(s) in the printed list (Petrolatum, Avobenzone, Octinoxate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Lip Balm with Sunscreen, SPF 30, 0.35 fl oz' (tube). Cross-check: all six actives match brand-site values exactly. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF (Dual Pack). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Lip-Balm-with-Sunscreen-Lip-Balm-SPF-30-0-35-Oz-Tube/23623346.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Lip Balm with Sunscreen, SPF 30, 0.35 fl oz' (tube). Cross-check: all six actives match brand-site values exactly. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF (Dual Pack). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Lip-Balm-with-Sunscreen-Lip-Balm-SPF-30-0-35-Oz-Tube/23623346.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2118,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Use Caution</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2126,23 +2132,23 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Glycerin, Bis-Diglyceryl Polyacyladipate-2, Water, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, C20-40 Alkyl Stearate, Magnesium Stearate</t>
+          <t>unknown — manual review needed: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, C20-40 Alkyl Stearate, Magnesium Stearate</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1 flagged ingredient(s) in the printed list (Bisabolol); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, C20-40 Alkyl Stearate, Magnesium Stearate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2180,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2188,7 +2194,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2198,17 +2204,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2246,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2254,7 +2260,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2264,17 +2270,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2312,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avoid (Moderate)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2320,23 +2326,23 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Sea Salt</t>
+          <t>unknown — manual review needed: Sea Salt</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference.</t>
+          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (25.4oz.). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (25.4oz.). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sea Salt. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2374,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2382,7 +2388,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Butane, Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Butane, Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2392,17 +2398,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 3 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butane, Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2440,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2448,7 +2454,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2458,17 +2464,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2506,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2514,7 +2520,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2524,17 +2530,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2572,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2580,7 +2586,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Hydrocortisone, Ceresin, Lanolin Alcohol, Glycerin, Menthoxypropanediol</t>
+          <t>unknown — manual review needed: Hydrocortisone, Ceresin, Lanolin Alcohol, Menthoxypropanediol</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2590,17 +2596,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 4 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Hydrocortisone, Ceresin, Lanolin Alcohol, Menthoxypropanediol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2638,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2646,7 +2652,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter, Glycerin</t>
+          <t>unknown — manual review needed: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2656,17 +2662,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Bisabolol); tier applies to the printed subset only. 5 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 4 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing (3 pack) Aquaphor Healing Balm Stick, 0.65 oz (listing 15374315224). Ingredients block sat under a collapsed section; expanded and read. Variant match: 3-pack. Cross-check: brand site text Petrolatum (30%) matches the active. Verbatim keeps the Active/Inactive label and the Purpose tag as printed. Other listings checked before this one: Walmart 0.65 oz Pack of 3 (7455005955), which the earlier pass reported with no ingredients block; not re-checked. Note: the Walmart listing is a 3-pack, and the Amazon and Walgreens listings found are single 0.65 oz sticks, not used. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Balm Stick (0.65oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart (3 pack) - https://www.walmart.com/ip/3-pack-Aquaphor-Healing-Balm-Stick-Skin-Protectant-0-65-Oz-Stick/15374315224.</t>
+          <t>Audit notes: Walmart listing (3 pack) Aquaphor Healing Balm Stick, 0.65 oz (listing 15374315224). Ingredients block sat under a collapsed section; expanded and read. Variant match: 3-pack. Cross-check: brand site text Petrolatum (30%) matches the active. Verbatim keeps the Active/Inactive label and the Purpose tag as printed. Other listings checked before this one: Walmart 0.65 oz Pack of 3 (7455005955), which the earlier pass reported with no ingredients block; not re-checked. Note: the Walmart listing is a 3-pack, and the Amazon and Walgreens listings found are single 0.65 oz sticks, not used. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart (3 pack) - https://www.walmart.com/ip/3-pack-Aquaphor-Healing-Balm-Stick-Skin-Protectant-0-65-Oz-Stick/15374315224.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2692,20 +2698,26 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ungradable</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Not graded: no ingredient text on the source page.</t>
+          <t>Ungradable: no ingredient text on the source page, so no tier is assigned.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>UNRESOLVED. Retailers checked: CVS (no Hand Mask result; brand shop lists Foot Masks only); Walgreens (no Hand Mask result); Ulta (blocked, Be Right Back page, could not load); Dermstore (no Aquaphor brand stocked); Amazon (only Advanced Therapy Repairing Hand Masks, 6 Masks x 0.7 FL OZ, B0B5FJFWW8, a 6-pack, not a single-unit match, not used); Target (A-86416643, Repairing Hand Mask 0.7 fl oz; Ingredients and Label info panels show no readable text, not used); Walmart (1791022082, Repairing Hand Masks 1 Pair; no readable Ingredients text after expanding, not used). Brand text Water, Glycerin, Urea is kept for reference. No verbatim ingredient text in the json; not graded.</t>
+          <t>UNRESOLVED. Retailers checked: CVS (no Hand Mask result; brand shop lists Foot Masks only); Walgreens (no Hand Mask result); Ulta (blocked, Be Right Back page, could not load); Dermstore (no Aquaphor brand stocked); Amazon (only Advanced Therapy Repairing Hand Masks, 6 Masks x 0.7 FL OZ, B0B5FJFWW8, a 6-pack, not a single-unit match, not used); Target (A-86416643, Repairing Hand Mask 0.7 fl oz; Ingredients and Label info panels show no readable text, not used); Walmart (1791022082, Repairing Hand Masks 1 Pair; no readable Ingredients text after expanding, not used). Brand text Water, Glycerin, Urea is kept for reference. No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2742,7 +2754,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2756,7 +2768,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Water, Glycerin, Urea, Hydrogenated Polyisobutene, Glyceryl Stearate, Butyrospermum Parkii (Shea) Butter, Persea Gratissima (Avocado) Oil, Tocopheryl Acetate, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Disodium EDTA, Hydroxyacetophenone</t>
+          <t>unknown — manual review needed: Urea, Hydrogenated Polyisobutene, Glyceryl Stearate, Butyrospermum Parkii (Shea) Butter, Persea Gratissima (Avocado) Oil, Tocopheryl Acetate, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Disodium EDTA, Hydroxyacetophenone</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2766,17 +2778,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Bisabolol, PEG-100 Stearate); tier applies to the printed subset only. 13 unknown ingredient(s) not in reference. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Audit notes: CVS listing Aquaphor Advanced Therapy Repairing Foot Masks, 1 Pair (prodid 648998). CVS shows the full list under Active Ingredients (uppercase) and Inactive Ingredients (title case); both contain the same 24 items in the same order. Title-case Inactive list used verbatim. Cross-check: first three (Water, Glycerin, Urea) match brand site. Target listing (0.7 fl oz) was not used; CVS 1-pair listing taken as the match for the brand row. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-advanced-therapy-repairing-foot-masks-1-pair-prodid-648998.</t>
+          <t>Audit notes: CVS listing Aquaphor Advanced Therapy Repairing Foot Masks, 1 Pair (prodid 648998). CVS shows the full list under Active Ingredients (uppercase) and Inactive Ingredients (title case); both contain the same 24 items in the same order. Title-case Inactive list used verbatim. Cross-check: first three (Water, Glycerin, Urea) match brand site. Target listing (0.7 fl oz) was not used; CVS 1-pair listing taken as the match for the brand row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Urea, Hydrogenated Polyisobutene, Glyceryl Stearate, Butyrospermum Parkii (Shea) Butter, Persea Gratissima (Avocado) Oil, Tocopheryl Acetate, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Disodium EDTA, Hydroxyacetophenone. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-advanced-therapy-repairing-foot-masks-1-pair-prodid-648998.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2820,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2822,7 +2834,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2832,17 +2844,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2886,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2888,7 +2900,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Butane, Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Butane, Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2898,17 +2910,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 3 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Audit notes: Amazon listing Aquaphor Advanced Therapy Ointment Body Spray, 6.2 OZ, Pack of 1 (B07TR75W9H). Variant match on size 6.2 oz. Cross-check: first three (Butane, Petrolatum, Mineral Oil) match brand site. CVS (3.7 oz) and Walmart (3.7 oz) listings were not used as they are a different size. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon - https://www.amazon.com/dp/B07TR75W9H.</t>
+          <t>Audit notes: Amazon listing Aquaphor Advanced Therapy Ointment Body Spray, 6.2 OZ, Pack of 1 (B07TR75W9H). Variant match on size 6.2 oz. Cross-check: first three (Butane, Petrolatum, Mineral Oil) match brand site. CVS (3.7 oz) and Walmart (3.7 oz) listings were not used as they are a different size. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butane, Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon - https://www.amazon.com/dp/B07TR75W9H.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2952,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2954,7 +2966,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2964,17 +2976,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor® Children's Healing Ointment (14oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor® Children's Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>
@@ -3000,20 +3012,26 @@
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ungradable</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Not graded: no ingredient text on the source page.</t>
+          <t>Ungradable: no ingredient text on the source page, so no tier is assigned.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>UNRESOLVED. No 2 x 3.5 oz listing found. Retailers checked: CVS (0.35 oz 2 CT, 1.75 oz, 3 oz No Touch, 5 oz, 7 oz; no 2 x 3.5 oz); Walgreens (0.35 oz x 2 pack, 1.75 oz, 7 oz, 14 oz; no 2 x 3.5 oz); Amazon (Multipack 3 x 2.8 oz, 3 x 1.75 oz, Value Pack 2 x 0.35 oz; no 2 x 3.5 oz); Walmart (0.35 oz x 2, 1.75 oz, 3 x 1.75 oz, 3 x 7 oz; no 2 x 3.5 oz); Target (1.75 oz, 2.8 oz jar; no 2 x 3.5 oz); Dermstore (no Aquaphor brand); Ulta blocked. Brand text Petrolatum (41%) kept for reference. No verbatim ingredient text in the json; not graded.</t>
+          <t>UNRESOLVED. No 2 x 3.5 oz listing found. Retailers checked: CVS (0.35 oz 2 CT, 1.75 oz, 3 oz No Touch, 5 oz, 7 oz; no 2 x 3.5 oz); Walgreens (0.35 oz x 2 pack, 1.75 oz, 7 oz, 14 oz; no 2 x 3.5 oz); Amazon (Multipack 3 x 2.8 oz, 3 x 1.75 oz, Value Pack 2 x 0.35 oz; no 2 x 3.5 oz); Walmart (0.35 oz x 2, 1.75 oz, 3 x 1.75 oz, 3 x 7 oz; no 2 x 3.5 oz); Target (1.75 oz, 2.8 oz jar; no 2 x 3.5 oz); Dermstore (no Aquaphor brand); Ulta blocked. Brand text Petrolatum (41%) kept for reference. No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3050,7 +3068,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Avoid (High Priority Swap)</t>
+          <t>ungradable</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -3064,7 +3082,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol, Glycerin</t>
+          <t>unknown — manual review needed: Ceresin, Lanolin Alcohol</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3074,17 +3092,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Ointment (14oz.). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>needs review</t>
         </is>
       </c>
     </row>

--- a/audits/aquaphor/aquaphor_audit.xlsx
+++ b/audits/aquaphor/aquaphor_audit.xlsx
@@ -540,12 +540,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'. Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'. Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -606,12 +606,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -672,12 +672,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -738,12 +738,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Audit notes: CONFLICT: CVS ingredients page (Aquaphor Moisturizing Cream, 1.89 OZ, prodid 923320) lists Water, Glycerin, Cetearyl Alcohol as the first three; brand site text lists Water, Glycerin, Caprylic/Capric Triglyceride. Both texts kept (brand_site_text unchanged). Grading uses the CVS verbatim list. Variant matches on name and size. Note the brand text may refer to a different formula or size. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-moisturizing-cream-1-89-oz-prodid-923320.</t>
+          <t>Audit notes: CONFLICT: CVS ingredients page (Aquaphor Moisturizing Cream, 1.89 OZ, prodid 923320) lists Water, Glycerin, Cetearyl Alcohol as the first three; brand site text lists Water, Glycerin, Caprylic/Capric Triglyceride. Both texts kept (brand_site_text unchanged). Grading uses the CVS verbatim list. Variant matches on name and size. Note the brand text may refer to a different formula or size. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-moisturizing-cream-1-89-oz-prodid-923320.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -870,12 +870,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride). Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (8oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride). Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (8oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -928,12 +928,12 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Aloe Vera, 0.17 oz' (single stick). Cross-check: first three match brand site. Brand-site list named Ricinus Communis Seed Oil; retailer uses Ricinus Communis (Castor) Seed Oil, same ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Aloe Barbadensis Leaf Juice Powder, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Aloe-Vera-0-17-oz-Stick/5322031840.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Aloe Vera, 0.17 oz' (single stick). Cross-check: first three match brand site. Brand-site list named Ricinus Communis Seed Oil; retailer uses Ricinus Communis (Castor) Seed Oil, same ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Aloe Barbadensis Leaf Juice Powder, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Aloe-Vera-0-17-oz-Stick/5322031840.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -986,12 +986,12 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Coconut Oil, 0.17 oz' (single stick). Cross-check: first three match brand site. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Coconut-Oil-0-17-oz-Stick/5415018384.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Coconut Oil, 0.17 oz' (single stick). Cross-check: first three match brand site. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Coconut-Oil-0-17-oz-Stick/5415018384.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069.</t>
+          <t>Audit notes: Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1110,12 +1110,12 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ungradable: 5 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>Ungradable: 5 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Diaper Rash Paste, Maximum Strength 40% Zinc Oxide, 3.5 oz'. Cross-check: brand-site Zinc Oxide (40%) matches the active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Octyldodecanol, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Butyrospermum Parkii (Shea) Butter. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Diaper-Rash-Paste-Maximum-Strength-40-Zinc-Oxide-Diaper-Rash-Cream-Diaper-Rash-Ointment-3-5-oz/299965693.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Diaper Rash Paste, Maximum Strength 40% Zinc Oxide, 3.5 oz'. Cross-check: brand-site Zinc Oxide (40%) matches the active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Octyldodecanol, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Butyrospermum Parkii (Shea) Butter. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Diaper-Rash-Paste-Maximum-Strength-40-Zinc-Oxide-Diaper-Rash-Cream-Diaper-Rash-Ointment-3-5-oz/299965693.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1. Escalation: PFAS.</t>
+          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Balm Stick for Dry Chapped Lips with Shea Butter, 0.17 oz'. Cross-check: first three match brand site. Dimethicone appears in this retailer list but not in the brand-site partial list; flagged for grader. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick (Dual Pack). D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/621710698.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Balm Stick for Dry Chapped Lips with Shea Butter, 0.17 oz'. Cross-check: first three match brand site. Dimethicone appears in this retailer list but not in the brand-site partial list; flagged for grader. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick (Dual Pack). D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/621710698.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Broad Spectrum SPF 30 Lip Repair Stick + Sunscreen 0.17 oz'. Cross-check: actives Avobenzone, Homosalate, Octisalate, Octocrylene match brand site. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, helianthus annuus (sunflower) seed oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Spf-30/1370153078.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Broad Spectrum SPF 30 Lip Repair Stick + Sunscreen 0.17 oz'. Cross-check: actives Avobenzone, Homosalate, Octisalate, Octocrylene match brand site. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, helianthus annuus (sunflower) seed oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Spf-30/1370153078.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Audit notes: Amazon listing Aquaphor Lip Balm, Lip Repair, SPF 30, 0.35 Oz Tube, Pack of 2 (B0D14XMH8R). Variant match: SPF 30 lip protectant, 2 x 0.35 oz. Actives match brand site text in name and percentage (Petrolatum 31%, Avobenzone 3%, Octinoxate 6.75%, Octisalate 4.5%, Octocrylene 2%, Oxybenzone 5.4%). Verbatim copied with Active and Inactive labels and Purpose tags as printed. Not verified on CVS, Walgreens, Ulta or Dermstore (CVS brand shop showed only a single lip repair plus sunscreen stick; Dermstore does not stock Aquaphor). Walmart pack was not used because it is a single SPF 30 tube. REVIEW: the row keeps product_type sunscreen from the prior pass. The grader escalates a cat. 1 flag to High Priority Swap only for leave-on skincare, so this row grades Avoid (Moderate) with 7 flags. The single Lip Protectant + SPF 30 row (lip product type, 7 flags) grades High Priority Swap. Both are leave-on tubes; Nina to confirm the type. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF 30. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate. Ingredient source: Amazon - https://www.amazon.com/dp/B0D14XMH8R.</t>
+          <t>Audit notes: Amazon listing Aquaphor Lip Balm, Lip Repair, SPF 30, 0.35 Oz Tube, Pack of 2 (B0D14XMH8R). Variant match: SPF 30 lip protectant, 2 x 0.35 oz. Actives match brand site text in name and percentage (Petrolatum 31%, Avobenzone 3%, Octinoxate 6.75%, Octisalate 4.5%, Octocrylene 2%, Oxybenzone 5.4%). Verbatim copied with Active and Inactive labels and Purpose tags as printed. Not verified on CVS, Walgreens, Ulta or Dermstore (CVS brand shop showed only a single lip repair plus sunscreen stick; Dermstore does not stock Aquaphor). Walmart pack was not used because it is a single SPF 30 tube. REVIEW: the row keeps product_type sunscreen from the prior pass. The grader escalates a cat. 1 flag to High Priority Swap only for leave-on skincare, so this row grades Avoid (Moderate) with 7 flags. The single Lip Protectant + SPF 30 row (lip product type, 7 flags) grades High Priority Swap. Both are leave-on tubes; Nina to confirm the type. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF 30. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate. Ingredient source: Amazon - https://www.amazon.com/dp/B0D14XMH8R.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair &amp; Protect SPF 30 Stick, 2pk, 0.35oz, Clear'. Cross-check: actives match brand site (Avobenzone 3, Homosalate 9, Octisalate 4.5, Octocrylene 9). Retailer 2-pack title, same product. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Protect-SPF-30-Stick-Dual-Pack-0-34oz-Pack-of-2-sticks/15665510241.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair &amp; Protect SPF 30 Stick, 2pk, 0.35oz, Clear'. Cross-check: actives match brand site (Avobenzone 3, Homosalate 9, Octisalate 4.5, Octocrylene 9). Retailer 2-pack title, same product. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Protect-SPF-30-Stick-Dual-Pack-0-34oz-Pack-of-2-sticks/15665510241.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1502,12 +1502,12 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1.</t>
+          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Lecithin, Ascorbyl Palmitate, C20-40 Alkyl Stearate, Magnesium Stearate, Glyceryl Stearate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Lecithin, Ascorbyl Palmitate, C20-40 Alkyl Stearate, Magnesium Stearate, Glyceryl Stearate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1. Escalation: PFAS.</t>
+          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Balm Stick, 0.17 oz, 2 Pack for Dry Chapped Lips'. Cross-check: first three match brand site. Same printed list as the single Lip Repair Stick. Dimethicone appears in retailer list only. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/304762780.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Balm Stick, 0.17 oz, 2 Pack for Dry Chapped Lips'. Cross-check: first three match brand site. Same printed list as the single Lip Repair Stick. Dimethicone appears in retailer list only. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/304762780.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1634,12 +1634,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ungradable: 4 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 4 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches. Identical printed text on 1 other product(s): Aquaphor® Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches. Identical printed text on 1 other product(s): Aquaphor® Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (Moderate)</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -1696,17 +1696,17 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Audit notes: Second-look verification. Amazon listing (B01NAFQIJ9, titled Aquaphor Baby Body Wash and Shampoo, 25.4 FL OZ, Fragrance Free, Tear Free) Ingredients block matches the user-supplied list word for word. CONFLICT with brand site text: brand text is Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate; Amazon/user list has Sodium Myreth Sulfate in position 3 and PEG-200 Hydrogenated Glyceryl Palmate in position 4. Both texts kept (brand_site_text unchanged). Earlier Walmart attribution for this row was not confirmed and has been replaced. Sodium Myreth Sulfate is a sulfate and is flagged by the grader. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (16.9 fl.oz). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sea Salt. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon (user-supplied, confirmed on listing) - https://www.amazon.com/dp/B01NAFQIJ9.</t>
+          <t>Audit notes: Second-look verification. Amazon listing (B01NAFQIJ9, titled Aquaphor Baby Body Wash and Shampoo, 25.4 FL OZ, Fragrance Free, Tear Free) Ingredients block matches the user-supplied list word for word. CONFLICT with brand site text: brand text is Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate; Amazon/user list has Sodium Myreth Sulfate in position 3 and PEG-200 Hydrogenated Glyceryl Palmate in position 4. Both texts kept (brand_site_text unchanged). Earlier Walmart attribution for this row was not confirmed and has been replaced. Sodium Myreth Sulfate is a sulfate and is flagged by the grader. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (16.9 fl.oz). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D8: one unknown ingredient, Use Caution floor applied (Sea Salt). Higher tier from other flags kept. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon (user-supplied, confirmed on listing) - https://www.amazon.com/dp/B01NAFQIJ9.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 fl oz'. Cross-check: first three match brand site. Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 8 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Lotion-3oz/19974261109.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 fl oz'. Cross-check: first three match brand site. Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 8 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Lotion-3oz/19974261109.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Sensitive Lotion, Baby Lotion, 8 fl oz'. Cross-check: first three match brand site (Water, Glycerin, Cetearyl Alcohol). Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Daily-Lotion-8-oz/19736656895.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Sensitive Lotion, Baby Lotion, 8 fl oz'. Cross-check: first three match brand site (Water, Glycerin, Cetearyl Alcohol). Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Daily-Lotion-8-oz/19736656895.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1894,12 +1894,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (7oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (7oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Lip Balm with Sunscreen, SPF 30, 0.35 fl oz' (tube). Cross-check: all six actives match brand-site values exactly. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF (Dual Pack). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Lip-Balm-with-Sunscreen-Lip-Balm-SPF-30-0-35-Oz-Tube/23623346.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Lip Balm with Sunscreen, SPF 30, 0.35 fl oz' (tube). Cross-check: all six actives match brand-site values exactly. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF (Dual Pack). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Lip-Balm-with-Sunscreen-Lip-Balm-SPF-30-0-35-Oz-Tube/23623346.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2138,12 +2138,12 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 1.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, C20-40 Alkyl Stearate, Magnesium Stearate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, C20-40 Alkyl Stearate, Magnesium Stearate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2204,12 +2204,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (Moderate)</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -2332,17 +2332,17 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Ungradable: 1 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (25.4oz.). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Sea Salt. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (25.4oz.). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D8: one unknown ingredient, Use Caution floor applied (Sea Salt). Higher tier from other flags kept. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2398,12 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butane, Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butane, Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Ungradable: 4 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 4 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Hydrocortisone, Ceresin, Lanolin Alcohol, Menthoxypropanediol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Hydrocortisone, Ceresin, Lanolin Alcohol, Menthoxypropanediol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2662,12 +2662,12 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Ungradable: 4 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 4 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing (3 pack) Aquaphor Healing Balm Stick, 0.65 oz (listing 15374315224). Ingredients block sat under a collapsed section; expanded and read. Variant match: 3-pack. Cross-check: brand site text Petrolatum (30%) matches the active. Verbatim keeps the Active/Inactive label and the Purpose tag as printed. Other listings checked before this one: Walmart 0.65 oz Pack of 3 (7455005955), which the earlier pass reported with no ingredients block; not re-checked. Note: the Walmart listing is a 3-pack, and the Amazon and Walgreens listings found are single 0.65 oz sticks, not used. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart (3 pack) - https://www.walmart.com/ip/3-pack-Aquaphor-Healing-Balm-Stick-Skin-Protectant-0-65-Oz-Stick/15374315224.</t>
+          <t>Audit notes: Walmart listing (3 pack) Aquaphor Healing Balm Stick, 0.65 oz (listing 15374315224). Ingredients block sat under a collapsed section; expanded and read. Variant match: 3-pack. Cross-check: brand site text Petrolatum (30%) matches the active. Verbatim keeps the Active/Inactive label and the Purpose tag as printed. Other listings checked before this one: Walmart 0.65 oz Pack of 3 (7455005955), which the earlier pass reported with no ingredients block; not re-checked. Note: the Walmart listing is a 3-pack, and the Amazon and Walgreens listings found are single 0.65 oz sticks, not used. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart (3 pack) - https://www.walmart.com/ip/3-pack-Aquaphor-Healing-Balm-Stick-Skin-Protectant-0-65-Oz-Stick/15374315224.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Audit notes: CVS listing Aquaphor Advanced Therapy Repairing Foot Masks, 1 Pair (prodid 648998). CVS shows the full list under Active Ingredients (uppercase) and Inactive Ingredients (title case); both contain the same 24 items in the same order. Title-case Inactive list used verbatim. Cross-check: first three (Water, Glycerin, Urea) match brand site. Target listing (0.7 fl oz) was not used; CVS 1-pair listing taken as the match for the brand row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Urea, Hydrogenated Polyisobutene, Glyceryl Stearate, Butyrospermum Parkii (Shea) Butter, Persea Gratissima (Avocado) Oil, Tocopheryl Acetate, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Disodium EDTA, Hydroxyacetophenone. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-advanced-therapy-repairing-foot-masks-1-pair-prodid-648998.</t>
+          <t>Audit notes: CVS listing Aquaphor Advanced Therapy Repairing Foot Masks, 1 Pair (prodid 648998). CVS shows the full list under Active Ingredients (uppercase) and Inactive Ingredients (title case); both contain the same 24 items in the same order. Title-case Inactive list used verbatim. Cross-check: first three (Water, Glycerin, Urea) match brand site. Target listing (0.7 fl oz) was not used; CVS 1-pair listing taken as the match for the brand row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Urea, Hydrogenated Polyisobutene, Glyceryl Stearate, Butyrospermum Parkii (Shea) Butter, Persea Gratissima (Avocado) Oil, Tocopheryl Acetate, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Disodium EDTA, Hydroxyacetophenone. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-advanced-therapy-repairing-foot-masks-1-pair-prodid-648998.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2910,12 +2910,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Audit notes: Amazon listing Aquaphor Advanced Therapy Ointment Body Spray, 6.2 OZ, Pack of 1 (B07TR75W9H). Variant match on size 6.2 oz. Cross-check: first three (Butane, Petrolatum, Mineral Oil) match brand site. CVS (3.7 oz) and Walmart (3.7 oz) listings were not used as they are a different size. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Butane, Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon - https://www.amazon.com/dp/B07TR75W9H.</t>
+          <t>Audit notes: Amazon listing Aquaphor Advanced Therapy Ointment Body Spray, 6.2 OZ, Pack of 1 (B07TR75W9H). Variant match on size 6.2 oz. Cross-check: first three (Butane, Petrolatum, Mineral Oil) match brand site. CVS (3.7 oz) and Walmart (3.7 oz) listings were not used as they are a different size. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butane, Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon - https://www.amazon.com/dp/B07TR75W9H.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor® Children's Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor® Children's Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredient(s) remain after D1 to D6, so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Unknown ingredient(s) remain after D1 to D6: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">

--- a/audits/aquaphor/aquaphor_audit.xlsx
+++ b/audits/aquaphor/aquaphor_audit.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -540,17 +540,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Pentylene Glycol, Sodium Cetearyl Sulfate); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'. Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'. Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -606,17 +606,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -672,17 +672,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -738,17 +738,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -804,17 +804,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Audit notes: CONFLICT: CVS ingredients page (Aquaphor Moisturizing Cream, 1.89 OZ, prodid 923320) lists Water, Glycerin, Cetearyl Alcohol as the first three; brand site text lists Water, Glycerin, Caprylic/Capric Triglyceride. Both texts kept (brand_site_text unchanged). Grading uses the CVS verbatim list. Variant matches on name and size. Note the brand text may refer to a different formula or size. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Cholesterol, Olea Europaea (Olive) Fruit Oil, pantolactone, Ricinus Communis (Castor) Seed Oil, Hydroxypropyl Starch Phosphate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-moisturizing-cream-1-89-oz-prodid-923320.</t>
+          <t>Audit notes: CONFLICT: CVS ingredients page (Aquaphor Moisturizing Cream, 1.89 OZ, prodid 923320) lists Water, Glycerin, Cetearyl Alcohol as the first three; brand site text lists Water, Glycerin, Caprylic/Capric Triglyceride. Both texts kept (brand_site_text unchanged). Grading uses the CVS verbatim list. Variant matches on name and size. Note the brand text may refer to a different formula or size. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-moisturizing-cream-1-89-oz-prodid-923320.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -870,17 +870,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Ungradable: 12 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 4. Escalation: carcinogen in leave-on.</t>
+          <t>4 flagged ingredient(s) in the printed list (Bisabolol, Pentylene Glycol, Sodium Cetearyl Sulfate); tier applies to the printed subset only. 12 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride). Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (8oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Ethylhexyl Stearate, Butyrospermum Parkii (Shea) Butter, Hydrogenated Coco-Glycerides, Glyceryl Stearate, Tapioca Starch, Cholesterol, Olea Europaea (Olive) Fruit Oil, Ricinus Communis (Castor) Seed Oil, pantolactone, Carrageenan, Hydrogenated Castor Oil. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride). Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (8oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -928,17 +928,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 11 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Aloe Vera, 0.17 oz' (single stick). Cross-check: first three match brand site. Brand-site list named Ricinus Communis Seed Oil; retailer uses Ricinus Communis (Castor) Seed Oil, same ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Aloe Barbadensis Leaf Juice Powder, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Aloe-Vera-0-17-oz-Stick/5322031840.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Aloe Vera, 0.17 oz' (single stick). Cross-check: first three match brand site. Brand-site list named Ricinus Communis Seed Oil; retailer uses Ricinus Communis (Castor) Seed Oil, same ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Aloe-Vera-0-17-oz-Stick/5322031840.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Puberty Safe</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -986,17 +986,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 9 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Coconut Oil, 0.17 oz' (single stick). Cross-check: first three match brand site. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Helianthus Annuus (Sunflower) Seed Oil, Ascorbyl Palmitate, Pantolactone. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Coconut-Oil-0-17-oz-Stick/5415018384.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Coconut Oil, 0.17 oz' (single stick). Cross-check: first three match brand site. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Coconut-Oil-0-17-oz-Stick/5415018384.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1052,17 +1052,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069.</t>
+          <t>Audit notes: Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1110,17 +1110,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Ungradable: 5 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 0.</t>
+          <t>No flagged ingredients in the printed list per reference and rubric conditionals. 5 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Diaper Rash Paste, Maximum Strength 40% Zinc Oxide, 3.5 oz'. Cross-check: brand-site Zinc Oxide (40%) matches the active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Octyldodecanol, Polyglyceryl-4 Diisostearate/Polyhydroxystearate/Sebacate, Magnesium Stearate, Butyrospermum Parkii (Shea) Butter. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Diaper-Rash-Paste-Maximum-Strength-40-Zinc-Oxide-Diaper-Rash-Cream-Diaper-Rash-Ointment-3-5-oz/299965693.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Diaper Rash Paste, Maximum Strength 40% Zinc Oxide, 3.5 oz'. Cross-check: brand-site Zinc Oxide (40%) matches the active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Diaper-Rash-Paste-Maximum-Strength-40-Zinc-Oxide-Diaper-Rash-Cream-Diaper-Rash-Ointment-3-5-oz/299965693.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: PFAS.</t>
+          <t>1 flagged ingredient(s) in the printed list (Dimethicone); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Balm Stick for Dry Chapped Lips with Shea Butter, 0.17 oz'. Cross-check: first three match brand site. Dimethicone appears in this retailer list but not in the brand-site partial list; flagged for grader. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick (Dual Pack). D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/621710698.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Balm Stick for Dry Chapped Lips with Shea Butter, 0.17 oz'. Cross-check: first three match brand site. Dimethicone appears in this retailer list but not in the brand-site partial list; flagged for grader. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick (Dual Pack). 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/621710698.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS.</t>
+          <t>5 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Broad Spectrum SPF 30 Lip Repair Stick + Sunscreen 0.17 oz'. Cross-check: actives Avobenzone, Homosalate, Octisalate, Octocrylene match brand site. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, helianthus annuus (sunflower) seed oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Spf-30/1370153078.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Broad Spectrum SPF 30 Lip Repair Stick + Sunscreen 0.17 oz'. Cross-check: actives Avobenzone, Homosalate, Octisalate, Octocrylene match brand site. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Spf-30/1370153078.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Petrolatum, Avobenzone, Octinoxate); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Audit notes: Amazon listing Aquaphor Lip Balm, Lip Repair, SPF 30, 0.35 Oz Tube, Pack of 2 (B0D14XMH8R). Variant match: SPF 30 lip protectant, 2 x 0.35 oz. Actives match brand site text in name and percentage (Petrolatum 31%, Avobenzone 3%, Octinoxate 6.75%, Octisalate 4.5%, Octocrylene 2%, Oxybenzone 5.4%). Verbatim copied with Active and Inactive labels and Purpose tags as printed. Not verified on CVS, Walgreens, Ulta or Dermstore (CVS brand shop showed only a single lip repair plus sunscreen stick; Dermstore does not stock Aquaphor). Walmart pack was not used because it is a single SPF 30 tube. REVIEW: the row keeps product_type sunscreen from the prior pass. The grader escalates a cat. 1 flag to High Priority Swap only for leave-on skincare, so this row grades Avoid (Moderate) with 7 flags. The single Lip Protectant + SPF 30 row (lip product type, 7 flags) grades High Priority Swap. Both are leave-on tubes; Nina to confirm the type. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF 30. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate. Ingredient source: Amazon - https://www.amazon.com/dp/B0D14XMH8R.</t>
+          <t>Audit notes: Amazon listing Aquaphor Lip Balm, Lip Repair, SPF 30, 0.35 Oz Tube, Pack of 2 (B0D14XMH8R). Variant match: SPF 30 lip protectant, 2 x 0.35 oz. Actives match brand site text in name and percentage (Petrolatum 31%, Avobenzone 3%, Octinoxate 6.75%, Octisalate 4.5%, Octocrylene 2%, Oxybenzone 5.4%). Verbatim copied with Active and Inactive labels and Purpose tags as printed. Not verified on CVS, Walgreens, Ulta or Dermstore (CVS brand shop showed only a single lip repair plus sunscreen stick; Dermstore does not stock Aquaphor). Walmart pack was not used because it is a single SPF 30 tube. REVIEW: the row keeps product_type sunscreen from the prior pass. The grader escalates a cat. 1 flag to High Priority Swap only for leave-on skincare, so this row grades Avoid (Moderate) with 7 flags. The single Lip Protectant + SPF 30 row (lip product type, 7 flags) grades High Priority Swap. Both are leave-on tubes; Nina to confirm the type. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF 30. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Amazon - https://www.amazon.com/dp/B0D14XMH8R.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS.</t>
+          <t>5 flagged ingredient(s) in the printed list (Avobenzone, Homosalate, Octisalate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair &amp; Protect SPF 30 Stick, 2pk, 0.35oz, Clear'. Cross-check: actives match brand site (Avobenzone 3, Homosalate 9, Octisalate 4.5, Octocrylene 9). Retailer 2-pack title, same product. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Helianthus Annuus (Sunflower) Seed Wax, Simmondsia Chinensis (Jojoba) Seed Oil, Copernicia Cerifera (Carnauba) Wax, Tocopheryl Acetate, Ascorbyl Palmitate, Helianthus Annuus (Sunflower) Seed Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Protect-SPF-30-Stick-Dual-Pack-0-34oz-Pack-of-2-sticks/15665510241.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair &amp; Protect SPF 30 Stick, 2pk, 0.35oz, Clear'. Cross-check: actives match brand site (Avobenzone 3, Homosalate 9, Octisalate 4.5, Octocrylene 9). Retailer 2-pack title, same product. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Protect-SPF-30-Stick-Dual-Pack-0-34oz-Pack-of-2-sticks/15665510241.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1440,17 +1440,17 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -1502,17 +1502,17 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Ungradable: 14 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1.</t>
+          <t>1 flagged ingredient(s) in the printed list (Bisabolol); tier applies to the printed subset only. 14 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, Lecithin, Ascorbyl Palmitate, C20-40 Alkyl Stearate, Magnesium Stearate, Glyceryl Stearate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1568,17 +1568,17 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1. Escalation: PFAS.</t>
+          <t>1 flagged ingredient(s) in the printed list (Dimethicone); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Balm Stick, 0.17 oz, 2 Pack for Dry Chapped Lips'. Cross-check: first three match brand site. Same printed list as the single Lip Repair Stick. Dimethicone appears in retailer list only. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Helianthus Annuus (Sunflower) Seed Wax, Hydrogenated Castor Oil, Tocopheryl Acetate, Simmondsia Chinensis (Jojoba) Seed Oil, Ascorbyl Palmitate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/304762780.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Balm Stick, 0.17 oz, 2 Pack for Dry Chapped Lips'. Cross-check: first three match brand site. Same printed list as the single Lip Repair Stick. Dimethicone appears in retailer list only. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/304762780.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1634,17 +1634,17 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Ungradable: 4 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Bisabolol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches. Identical printed text on 1 other product(s): Aquaphor® Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches. Identical printed text on 1 other product(s): Aquaphor® Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Audit notes: Second-look verification. Amazon listing (B01NAFQIJ9, titled Aquaphor Baby Body Wash and Shampoo, 25.4 FL OZ, Fragrance Free, Tear Free) Ingredients block matches the user-supplied list word for word. CONFLICT with brand site text: brand text is Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate; Amazon/user list has Sodium Myreth Sulfate in position 3 and PEG-200 Hydrogenated Glyceryl Palmate in position 4. Both texts kept (brand_site_text unchanged). Earlier Walmart attribution for this row was not confirmed and has been replaced. Sodium Myreth Sulfate is a sulfate and is flagged by the grader. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (16.9 fl.oz). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D8: one unknown ingredient, Use Caution floor applied (Sea Salt). Higher tier from other flags kept. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon (user-supplied, confirmed on listing) - https://www.amazon.com/dp/B01NAFQIJ9.</t>
+          <t>Audit notes: Second-look verification. Amazon listing (B01NAFQIJ9, titled Aquaphor Baby Body Wash and Shampoo, 25.4 FL OZ, Fragrance Free, Tear Free) Ingredients block matches the user-supplied list word for word. CONFLICT with brand site text: brand text is Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate; Amazon/user list has Sodium Myreth Sulfate in position 3 and PEG-200 Hydrogenated Glyceryl Palmate in position 4. Both texts kept (brand_site_text unchanged). Earlier Walmart attribution for this row was not confirmed and has been replaced. Sodium Myreth Sulfate is a sulfate and is flagged by the grader. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (16.9 fl.oz). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon (user-supplied, confirmed on listing) - https://www.amazon.com/dp/B01NAFQIJ9.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1762,17 +1762,17 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 fl oz'. Cross-check: first three match brand site. Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 8 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Lotion-3oz/19974261109.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 fl oz'. Cross-check: first three match brand site. Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 8 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Lotion-3oz/19974261109.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1828,17 +1828,17 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Ungradable: 8 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Phenoxyethanol, Sodium Cetearyl Sulfate, Ethylhexylglycerin); tier applies to the printed subset only. 8 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Sensitive Lotion, Baby Lotion, 8 fl oz'. Cross-check: first three match brand site (Water, Glycerin, Cetearyl Alcohol). Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ethylhexyl Stearate, Caprylic/Capric Triglyceride, Dicaprylyl Ether, Hydroxypropyl Starch Phosphate, Pantolactone, Cholesterol, Phytosphingosine, Glycine Soja (Soybean) Oil. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Daily-Lotion-8-oz/19736656895.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Sensitive Lotion, Baby Lotion, 8 fl oz'. Cross-check: first three match brand site (Water, Glycerin, Cetearyl Alcohol). Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Daily-Lotion-8-oz/19736656895.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1960,17 +1960,17 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (7oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (7oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>UNRESOLVED. Size mismatch. Brand row is 3 oz. Retailers checked: CVS (Aquaphor Baby Diaper Rash Paste 3.5 oz only, not a cream match); Walgreens (Aquaphor Baby Diaper Rash Cream with Zinc Oxide 3.5 oz, not a 3 oz match); Amazon (Baby Diaper Rash Cream with Zinc Oxide Multipack 3 x 3.5 oz and Diaper Rash Paste 3.5 oz, not a 3 oz match); Dermstore (no Aquaphor brand); Walmart (3.5 oz only per earlier pass). Ulta blocked. Brand text Zinc Oxide (15%) kept for reference. No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>UNRESOLVED. Size mismatch. Brand row is 3 oz. Retailers checked: CVS (Aquaphor Baby Diaper Rash Paste 3.5 oz only, not a cream match); Walgreens (Aquaphor Baby Diaper Rash Cream with Zinc Oxide 3.5 oz, not a 3 oz match); Amazon (Baby Diaper Rash Cream with Zinc Oxide Multipack 3 x 3.5 oz and Diaper Rash Paste 3.5 oz, not a 3 oz match); Dermstore (no Aquaphor brand); Walmart (3.5 oz only per earlier pass). Ulta blocked. Brand text Zinc Oxide (15%) kept for reference. No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Ungradable: 9 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 7. Escalation: carcinogen in leave-on.</t>
+          <t>7 flagged ingredient(s) in the printed list (Petrolatum, Avobenzone, Octinoxate); tier applies to the printed subset only. 9 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Lip Balm with Sunscreen, SPF 30, 0.35 fl oz' (tube). Cross-check: all six actives match brand-site values exactly. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF (Dual Pack). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: C18-38 Alkyl Hydroxystearoyl Stearate, Octyldodecanol, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Butyrospermum Parkii (Shea) Butter, Tocopheryl Acetate, Hydrogenated Castor Oil, C20-40 Alkyl Stearate, Magnesium Stearate. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Lip-Balm-with-Sunscreen-Lip-Balm-SPF-30-0-35-Oz-Tube/23623346.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Lip Balm with Sunscreen, SPF 30, 0.35 fl oz' (tube). Cross-check: all six actives match brand-site values exactly. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF (Dual Pack). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Lip-Balm-with-Sunscreen-Lip-Balm-SPF-30-0-35-Oz-Tube/23623346.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -2138,17 +2138,17 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 1.</t>
+          <t>1 flagged ingredient(s) in the printed list (Bisabolol); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Octyldodecanol, C18-38 Alkyl Hydroxystearoyl Stearate, Ricinus Communis (Castor) Seed Oil, Caprylic/Capric Triglyceride, Bis-Diglyceryl Polyacyladipate-2, Butyrospermum Parkii (Shea) Butter, Hydrogenated Castor Oil, Tocopheryl Acetate, Sodium Ascorbyl Phosphate, C20-40 Alkyl Stearate, Magnesium Stearate. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -2204,17 +2204,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -2270,17 +2270,17 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2332,12 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference.</t>
+          <t>5 flagged ingredient(s) in the printed list (Sodium Myreth Sulfate, PEG-200 Hydrogenated Glyceryl Palmate, Cocamidopropyl Betaine); tier applies to the printed subset only. 1 unknown ingredient(s) not in reference, excluded from grade.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (25.4oz.). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). D8: one unknown ingredient, Use Caution floor applied (Sea Salt). Higher tier from other flags kept. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (25.4oz.). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -2398,17 +2398,17 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butane, Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -2464,17 +2464,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2530,17 +2530,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Ungradable: 4 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Hydrocortisone, Ceresin, Lanolin Alcohol, Menthoxypropanediol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -2662,17 +2662,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Ungradable: 4 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 2. Escalation: carcinogen in leave-on.</t>
+          <t>2 flagged ingredient(s) in the printed list (Petrolatum, Bisabolol); tier applies to the printed subset only. 4 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing (3 pack) Aquaphor Healing Balm Stick, 0.65 oz (listing 15374315224). Ingredients block sat under a collapsed section; expanded and read. Variant match: 3-pack. Cross-check: brand site text Petrolatum (30%) matches the active. Verbatim keeps the Active/Inactive label and the Purpose tag as printed. Other listings checked before this one: Walmart 0.65 oz Pack of 3 (7455005955), which the earlier pass reported with no ingredients block; not re-checked. Note: the Walmart listing is a 3-pack, and the Amazon and Walgreens listings found are single 0.65 oz sticks, not used. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Caprylic/Capric Triglyceride, Persea Gratissima (Avocado) Oil, Microcrystalline Wax, Butyrospermum Parkii (Shea) Butter. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart (3 pack) - https://www.walmart.com/ip/3-pack-Aquaphor-Healing-Balm-Stick-Skin-Protectant-0-65-Oz-Stick/15374315224.</t>
+          <t>Audit notes: Walmart listing (3 pack) Aquaphor Healing Balm Stick, 0.65 oz (listing 15374315224). Ingredients block sat under a collapsed section; expanded and read. Variant match: 3-pack. Cross-check: brand site text Petrolatum (30%) matches the active. Verbatim keeps the Active/Inactive label and the Purpose tag as printed. Other listings checked before this one: Walmart 0.65 oz Pack of 3 (7455005955), which the earlier pass reported with no ingredients block; not re-checked. Note: the Walmart listing is a 3-pack, and the Amazon and Walgreens listings found are single 0.65 oz sticks, not used. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart (3 pack) - https://www.walmart.com/ip/3-pack-Aquaphor-Healing-Balm-Stick-Skin-Protectant-0-65-Oz-Stick/15374315224.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>UNRESOLVED. Retailers checked: CVS (no Hand Mask result; brand shop lists Foot Masks only); Walgreens (no Hand Mask result); Ulta (blocked, Be Right Back page, could not load); Dermstore (no Aquaphor brand stocked); Amazon (only Advanced Therapy Repairing Hand Masks, 6 Masks x 0.7 FL OZ, B0B5FJFWW8, a 6-pack, not a single-unit match, not used); Target (A-86416643, Repairing Hand Mask 0.7 fl oz; Ingredients and Label info panels show no readable text, not used); Walmart (1791022082, Repairing Hand Masks 1 Pair; no readable Ingredients text after expanding, not used). Brand text Water, Glycerin, Urea is kept for reference. No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>UNRESOLVED. Retailers checked: CVS (no Hand Mask result; brand shop lists Foot Masks only); Walgreens (no Hand Mask result); Ulta (blocked, Be Right Back page, could not load); Dermstore (no Aquaphor brand stocked); Amazon (only Advanced Therapy Repairing Hand Masks, 6 Masks x 0.7 FL OZ, B0B5FJFWW8, a 6-pack, not a single-unit match, not used); Target (A-86416643, Repairing Hand Mask 0.7 fl oz; Ingredients and Label info panels show no readable text, not used); Walmart (1791022082, Repairing Hand Masks 1 Pair; no readable Ingredients text after expanding, not used). Brand text Water, Glycerin, Urea is kept for reference. No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -2778,17 +2778,17 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Ungradable: 11 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 5. Escalation: PFAS, carcinogen in leave-on.</t>
+          <t>5 flagged ingredient(s) in the printed list (Dimethicone, Bisabolol, PEG-100 Stearate); tier applies to the printed subset only. 11 unknown ingredient(s) not in reference, excluded from grade. Escalation: PFAS, carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Audit notes: CVS listing Aquaphor Advanced Therapy Repairing Foot Masks, 1 Pair (prodid 648998). CVS shows the full list under Active Ingredients (uppercase) and Inactive Ingredients (title case); both contain the same 24 items in the same order. Title-case Inactive list used verbatim. Cross-check: first three (Water, Glycerin, Urea) match brand site. Target listing (0.7 fl oz) was not used; CVS 1-pair listing taken as the match for the brand row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Urea, Hydrogenated Polyisobutene, Glyceryl Stearate, Butyrospermum Parkii (Shea) Butter, Persea Gratissima (Avocado) Oil, Tocopheryl Acetate, Caprylic/Capric Triglyceride, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Sodium Hydroxide, Disodium EDTA, Hydroxyacetophenone. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-advanced-therapy-repairing-foot-masks-1-pair-prodid-648998.</t>
+          <t>Audit notes: CVS listing Aquaphor Advanced Therapy Repairing Foot Masks, 1 Pair (prodid 648998). CVS shows the full list under Active Ingredients (uppercase) and Inactive Ingredients (title case); both contain the same 24 items in the same order. Title-case Inactive list used verbatim. Cross-check: first three (Water, Glycerin, Urea) match brand site. Target listing (0.7 fl oz) was not used; CVS 1-pair listing taken as the match for the brand row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-advanced-therapy-repairing-foot-masks-1-pair-prodid-648998.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -2844,17 +2844,17 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -2910,17 +2910,17 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Ungradable: 3 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 3 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Audit notes: Amazon listing Aquaphor Advanced Therapy Ointment Body Spray, 6.2 OZ, Pack of 1 (B07TR75W9H). Variant match on size 6.2 oz. Cross-check: first three (Butane, Petrolatum, Mineral Oil) match brand site. CVS (3.7 oz) and Walmart (3.7 oz) listings were not used as they are a different size. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Butane, Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon - https://www.amazon.com/dp/B07TR75W9H.</t>
+          <t>Audit notes: Amazon listing Aquaphor Advanced Therapy Ointment Body Spray, 6.2 OZ, Pack of 1 (B07TR75W9H). Variant match on size 6.2 oz. Cross-check: first three (Butane, Petrolatum, Mineral Oil) match brand site. CVS (3.7 oz) and Walmart (3.7 oz) listings were not used as they are a different size. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon - https://www.amazon.com/dp/B07TR75W9H.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -2976,17 +2976,17 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor® Children's Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor® Children's Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>UNRESOLVED. No 2 x 3.5 oz listing found. Retailers checked: CVS (0.35 oz 2 CT, 1.75 oz, 3 oz No Touch, 5 oz, 7 oz; no 2 x 3.5 oz); Walgreens (0.35 oz x 2 pack, 1.75 oz, 7 oz, 14 oz; no 2 x 3.5 oz); Amazon (Multipack 3 x 2.8 oz, 3 x 1.75 oz, Value Pack 2 x 0.35 oz; no 2 x 3.5 oz); Walmart (0.35 oz x 2, 1.75 oz, 3 x 1.75 oz, 3 x 7 oz; no 2 x 3.5 oz); Target (1.75 oz, 2.8 oz jar; no 2 x 3.5 oz); Dermstore (no Aquaphor brand); Ulta blocked. Brand text Petrolatum (41%) kept for reference. No verbatim ingredient text in the json; not graded (D7 ungradable).</t>
+          <t>UNRESOLVED. No 2 x 3.5 oz listing found. Retailers checked: CVS (0.35 oz 2 CT, 1.75 oz, 3 oz No Touch, 5 oz, 7 oz; no 2 x 3.5 oz); Walgreens (0.35 oz x 2 pack, 1.75 oz, 7 oz, 14 oz; no 2 x 3.5 oz); Amazon (Multipack 3 x 2.8 oz, 3 x 1.75 oz, Value Pack 2 x 0.35 oz; no 2 x 3.5 oz); Walmart (0.35 oz x 2, 1.75 oz, 3 x 1.75 oz, 3 x 7 oz; no 2 x 3.5 oz); Target (1.75 oz, 2.8 oz jar; no 2 x 3.5 oz); Dermstore (no Aquaphor brand); Ulta blocked. Brand text Petrolatum (41%) kept for reference. No verbatim ingredient text in the json; not graded.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ungradable</t>
+          <t>Avoid (High Priority Swap)</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -3092,17 +3092,17 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Ungradable: 2 unknown ingredients remain (D7, two or more), so no tier is assigned. Partial flags recorded: 3. Escalation: carcinogen in leave-on.</t>
+          <t>3 flagged ingredient(s) in the printed list (Petrolatum, Mineral Oil, Bisabolol); tier applies to the printed subset only. 2 unknown ingredient(s) not in reference, excluded from grade. Escalation: carcinogen in leave-on.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. D7: ungradable. Two or more unknown ingredients remain: Ceresin, Lanolin Alcohol. D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>needs review</t>
+          <t>complete</t>
         </is>
       </c>
     </row>

--- a/audits/aquaphor/aquaphor_audit.xlsx
+++ b/audits/aquaphor/aquaphor_audit.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'. Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 8 oz Tube'. Cross-check: first three ingredients (Water, Glycerin, Caprylic/Capric Triglyceride) match brand site. Printed list uses a non-ASCII hyphen in 'Coco-Glycerides'. Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-8-oz/19840324444.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 3 fl oz Tube'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-3-oz/19860762998.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 8 fl oz Pump Bottle'. Cross-check: first three (Water, Glycerin, Cetearyl Alcohol) match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (16oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-8-oz/19897618953.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Daily Hydrating Face and Body Lotion, 16 fl oz Pump Bottle'. Cross-check: first three match brand site. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Moisturizing Cream (1.89oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Hydrating-Daily-Lotion-16-oz/19832201924.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Audit notes: CONFLICT: CVS ingredients page (Aquaphor Moisturizing Cream, 1.89 OZ, prodid 923320) lists Water, Glycerin, Cetearyl Alcohol as the first three; brand site text lists Water, Glycerin, Caprylic/Capric Triglyceride. Both texts kept (brand_site_text unchanged). Grading uses the CVS verbatim list. Variant matches on name and size. Note the brand text may refer to a different formula or size. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-moisturizing-cream-1-89-oz-prodid-923320.</t>
+          <t>Audit notes: CONFLICT: CVS ingredients page (Aquaphor Moisturizing Cream, 1.89 OZ, prodid 923320) lists Water, Glycerin, Cetearyl Alcohol as the first three; brand site text lists Water, Glycerin, Caprylic/Capric Triglyceride. Both texts kept (brand_site_text unchanged). Grading uses the CVS verbatim list. Variant matches on name and size. Note the brand text may refer to a different formula or size. Identical printed text on 3 other product(s): Aquaphor® Hydrating Daily Lotion (3oz.); Aquaphor® Hydrating Daily Lotion (8oz.); Aquaphor® Hydrating Daily Lotion (16oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-moisturizing-cream-1-89-oz-prodid-923320.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride). Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (8oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Moisturizing Face and Body Cream, 16 oz Jar'. Cross-check: first three ingredients match brand site (Water, Glycerin, Caprylic/Capric Triglyceride). Identical printed text on 1 other product(s): Aquaphor® Moisturizing Cream (8oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 12 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Moisturizing-Cream-16-oz/19815416701.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Aloe Vera, 0.17 oz' (single stick). Cross-check: first three match brand site. Brand-site list named Ricinus Communis Seed Oil; retailer uses Ricinus Communis (Castor) Seed Oil, same ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Aloe-Vera-0-17-oz-Stick/5322031840.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Aloe Vera, 0.17 oz' (single stick). Cross-check: first three match brand site. Brand-site list named Ricinus Communis Seed Oil; retailer uses Ricinus Communis (Castor) Seed Oil, same ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Aloe-Vera-0-17-oz-Stick/5322031840.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Puberty Safe</t>
+          <t>Use Caution</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -991,7 +991,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Coconut Oil, 0.17 oz' (single stick). Cross-check: first three match brand site. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Coconut-Oil-0-17-oz-Stick/5415018384.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Naturally Inspired Lip Repair Balm Stick for Very Dry Lips with Coconut Oil, 0.17 oz' (single stick). Cross-check: first three match brand site. 9 unknown ingredient(s) excluded from flags (2026-10-17). Puberty Safe requires zero unknown ingredients: 9 unknown ingredient(s) move this product to Use Caution (2026-10-17 practitioner rule). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Naturally-Inspired-Lip-Repair-Lip-Balm-Stick-with-Coconut-Oil-0-17-oz-Stick/5415018384.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069.</t>
+          <t>Audit notes: Walmart Aquaphor Baby Advanced Therapy Healing Ointment 7 oz listing; Drug Facts ingredients block. Retailer listing titled 'Aquaphor Baby Advanced Therapy Healing Ointment, 7 oz' matches product variant. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Advanced-Therapy-Skin-Protectant-7-Oz-Tube/52639069.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Diaper Rash Paste, Maximum Strength 40% Zinc Oxide, 3.5 oz'. Cross-check: brand-site Zinc Oxide (40%) matches the active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Diaper-Rash-Paste-Maximum-Strength-40-Zinc-Oxide-Diaper-Rash-Cream-Diaper-Rash-Ointment-3-5-oz/299965693.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Diaper Rash Paste, Maximum Strength 40% Zinc Oxide, 3.5 oz'. Cross-check: brand-site Zinc Oxide (40%) matches the active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 5 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Diaper-Rash-Paste-Maximum-Strength-40-Zinc-Oxide-Diaper-Rash-Cream-Diaper-Rash-Ointment-3-5-oz/299965693.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Balm Stick for Dry Chapped Lips with Shea Butter, 0.17 oz'. Cross-check: first three match brand site. Dimethicone appears in this retailer list but not in the brand-site partial list; flagged for grader. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick (Dual Pack). 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/621710698.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Balm Stick for Dry Chapped Lips with Shea Butter, 0.17 oz'. Cross-check: first three match brand site. Dimethicone appears in this retailer list but not in the brand-site partial list; flagged for grader. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick (Dual Pack). 9 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/621710698.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Broad Spectrum SPF 30 Lip Repair Stick + Sunscreen 0.17 oz'. Cross-check: actives Avobenzone, Homosalate, Octisalate, Octocrylene match brand site. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Spf-30/1370153078.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Broad Spectrum SPF 30 Lip Repair Stick + Sunscreen 0.17 oz'. Cross-check: actives Avobenzone, Homosalate, Octisalate, Octocrylene match brand site. 11 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Spf-30/1370153078.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Audit notes: Amazon listing Aquaphor Lip Balm, Lip Repair, SPF 30, 0.35 Oz Tube, Pack of 2 (B0D14XMH8R). Variant match: SPF 30 lip protectant, 2 x 0.35 oz. Actives match brand site text in name and percentage (Petrolatum 31%, Avobenzone 3%, Octinoxate 6.75%, Octisalate 4.5%, Octocrylene 2%, Oxybenzone 5.4%). Verbatim copied with Active and Inactive labels and Purpose tags as printed. Not verified on CVS, Walgreens, Ulta or Dermstore (CVS brand shop showed only a single lip repair plus sunscreen stick; Dermstore does not stock Aquaphor). Walmart pack was not used because it is a single SPF 30 tube. REVIEW: the row keeps product_type sunscreen from the prior pass. The grader escalates a cat. 1 flag to High Priority Swap only for leave-on skincare, so this row grades Avoid (Moderate) with 7 flags. The single Lip Protectant + SPF 30 row (lip product type, 7 flags) grades High Priority Swap. Both are leave-on tubes; Nina to confirm the type. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF 30. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Amazon - https://www.amazon.com/dp/B0D14XMH8R.</t>
+          <t>Audit notes: Amazon listing Aquaphor Lip Balm, Lip Repair, SPF 30, 0.35 Oz Tube, Pack of 2 (B0D14XMH8R). Variant match: SPF 30 lip protectant, 2 x 0.35 oz. Actives match brand site text in name and percentage (Petrolatum 31%, Avobenzone 3%, Octinoxate 6.75%, Octisalate 4.5%, Octocrylene 2%, Oxybenzone 5.4%). Verbatim copied with Active and Inactive labels and Purpose tags as printed. Not verified on CVS, Walgreens, Ulta or Dermstore (CVS brand shop showed only a single lip repair plus sunscreen stick; Dermstore does not stock Aquaphor). Walmart pack was not used because it is a single SPF 30 tube. REVIEW: the row keeps product_type sunscreen from the prior pass. The grader escalates a cat. 1 flag to High Priority Swap only for leave-on skincare, so this row grades Avoid (Moderate) with 7 flags. The single Lip Protectant + SPF 30 row (lip product type, 7 flags) grades High Priority Swap. Both are leave-on tubes; Nina to confirm the type. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF 30. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Amazon - https://www.amazon.com/dp/B0D14XMH8R.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair &amp; Protect SPF 30 Stick, 2pk, 0.35oz, Clear'. Cross-check: actives match brand site (Avobenzone 3, Homosalate 9, Octisalate 4.5, Octocrylene 9). Retailer 2-pack title, same product. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Protect-SPF-30-Stick-Dual-Pack-0-34oz-Pack-of-2-sticks/15665510241.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair &amp; Protect SPF 30 Stick, 2pk, 0.35oz, Clear'. Cross-check: actives match brand site (Avobenzone 3, Homosalate 9, Octisalate 4.5, Octocrylene 9). Retailer 2-pack title, same product. 11 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Protect-SPF-30-Stick-Dual-Pack-0-34oz-Pack-of-2-sticks/15665510241.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Healing Ointment for Dry, Chapped or Irritated Skin, Hypoallergenic, 14 oz'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Healing-Ointment-Skin-Protectant-14oz-Jar/1612392187.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Lip Repair Ointment, .35 fl oz' (tube). Cross-check: first three match brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 14 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Aquaphor-Lip-Repair-Ointment-Tube-35-fl-oz-0-35-Fl-Oz/662828970.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Balm Stick, 0.17 oz, 2 Pack for Dry Chapped Lips'. Cross-check: first three match brand site. Same printed list as the single Lip Repair Stick. Dimethicone appears in retailer list only. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/304762780.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Balm Stick, 0.17 oz, 2 Pack for Dry Chapped Lips'. Cross-check: first three match brand site. Same printed list as the single Lip Repair Stick. Dimethicone appears in retailer list only. Identical printed text on 1 other product(s): Aquaphor® Lip Repair Stick. 9 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Stick-Lip-Balm-for-Dry-Chapped-Lips/304762780.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches. Identical printed text on 1 other product(s): Aquaphor® Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Balm Stick with Avocado Oil and Shea Butter, 0.65 oz'. Cross-check: brand-site Petrolatum (30%) matches. Identical printed text on 1 other product(s): Aquaphor® Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Balm-Stick-0-65-Oz/677483860.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Audit notes: Second-look verification. Amazon listing (B01NAFQIJ9, titled Aquaphor Baby Body Wash and Shampoo, 25.4 FL OZ, Fragrance Free, Tear Free) Ingredients block matches the user-supplied list word for word. CONFLICT with brand site text: brand text is Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate; Amazon/user list has Sodium Myreth Sulfate in position 3 and PEG-200 Hydrogenated Glyceryl Palmate in position 4. Both texts kept (brand_site_text unchanged). Earlier Walmart attribution for this row was not confirmed and has been replaced. Sodium Myreth Sulfate is a sulfate and is flagged by the grader. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (16.9 fl.oz). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon (user-supplied, confirmed on listing) - https://www.amazon.com/dp/B01NAFQIJ9.</t>
+          <t>Audit notes: Second-look verification. Amazon listing (B01NAFQIJ9, titled Aquaphor Baby Body Wash and Shampoo, 25.4 FL OZ, Fragrance Free, Tear Free) Ingredients block matches the user-supplied list word for word. CONFLICT with brand site text: brand text is Water, Decyl Glucoside, PEG-200 Hydrogenated Glyceryl Palmate; Amazon/user list has Sodium Myreth Sulfate in position 3 and PEG-200 Hydrogenated Glyceryl Palmate in position 4. Both texts kept (brand_site_text unchanged). Earlier Walmart attribution for this row was not confirmed and has been replaced. Sodium Myreth Sulfate is a sulfate and is flagged by the grader. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (16.9 fl.oz). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). 1 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon (user-supplied, confirmed on listing) - https://www.amazon.com/dp/B01NAFQIJ9.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 fl oz'. Cross-check: first three match brand site. Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 8 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Lotion-3oz/19974261109.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 fl oz'. Cross-check: first three match brand site. Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 8 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Lotion-3oz/19974261109.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Sensitive Lotion, Baby Lotion, 8 fl oz'. Cross-check: first three match brand site (Water, Glycerin, Cetearyl Alcohol). Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Daily-Lotion-8-oz/19736656895.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Sensitive Lotion, Baby Lotion, 8 fl oz'. Cross-check: first three match brand site (Water, Glycerin, Cetearyl Alcohol). Identical printed text on 1 other product(s): Aquaphor Baby Sensitive Lotion, Baby Lotion, 3 Fl Oz. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 8 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Sensitive-Daily-Lotion-8-oz/19736656895.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Advanced Therapy Healing Ointment Skin Protectant, 3 oz' (plastic bottle). Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Newborn-Skin-Care-and-Diaper-Rash-3-oz-Plastic-Bottle/11997291.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (7oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Healing Ointment, 14 oz, for Diaper Rash and Skin Care'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor Healing Ointment® (7oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-14-oz/44997847.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Lip Balm with Sunscreen, SPF 30, 0.35 fl oz' (tube). Cross-check: all six actives match brand-site values exactly. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF (Dual Pack). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Lip-Balm-with-Sunscreen-Lip-Balm-SPF-30-0-35-Oz-Tube/23623346.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Lip Balm with Sunscreen, SPF 30, 0.35 fl oz' (tube). Cross-check: all six actives match brand-site values exactly. Identical printed text on 1 other product(s): Aquaphor® Lip Protectant + SPF (Dual Pack). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 9 unknown ingredient(s) excluded from flags (2026-10-17). Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Lip-Balm-with-Sunscreen-Lip-Balm-SPF-30-0-35-Oz-Tube/23623346.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Lip Repair Ointment, 0.35 fl oz, 2 Pack, with Shea Butter'. Cross-check: first three match brand site. Printed 2-pack list differs slightly from the single-tube listing (no Lecithin, Ascorbyl Palmitate, Glyceryl Stearate, Glyceryl Oleate, or Citric Acid), so the 2-pack list is used for the 2-pack row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Lip-Repair-Ointment-Long-lasting-Moisture-to-Soothe-Dry-Chapped-Lips-0-35-oz-Pack-of-2-tubes/374868721.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment for Teething, Drool and Diaper Rash, Travel Size, 0.35 oz, 2 Pack'. Same product, 2-pack size matches. Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-On-the-go/25868523.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Baby Healing Ointment Skin Protectant, 1.75 OZ' (travel size). Cross-check: active Petrolatum 41% matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Healing-Ointment-Baby-Skin-Care-and-Diaper-Rash-Travel-Size/16777958.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (25.4oz.). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). 1 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Baby Wash &amp; Shampoo, 16.9 fl oz, Fragrance Free Tear Free'. Cross-check: first three match brand site. Same printed list as the 25.4 fl oz listing. Identical printed text on 1 other product(s): Aquaphor® Baby Wash &amp; Shampoo (25.4oz.). Sulfate-flagged ingredient in a daily rinse-off product: minimum Avoid (Mild) (rubric, shampoos). 1 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Baby-Wash-Shampoo-16-9-oz/164941301.</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Body Spray, 3.7 oz, Skin Relief, Fragrance Free, Easy-to-Apply'. Cross-check: first three ingredients (Butane, Petrolatum, Mineral Oil) match brand site. Page also shows a stray 'salicylic acid' table row that belongs to another listing; not used as an ingredient. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 3 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Ointment-Body-Spray-3-7-Oz-Spray-Can/817364182.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Advanced Therapy Skin Protectant, Travel Size, 0.25 Oz Jar'. Variant match on size. Cross-check: active Petrolatum (41%) matches brand site. Printed label has a missing comma after Panthenol and a diaper-rash purpose line; kept as printed. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-0-25-Oz-Jar/40170172.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant ... Touch-Free, 3 oz'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-3-oz/40816008.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Children's Itch Relief Ointment, 1% Hydrocortisone Anti-Itch Cream, Fast-Acting, 1 oz'. Cross-check: brand site Hydrocortisone (1%) matches first active. Drug-labeled product: hydrocortisone is an OTC active. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Children-s-Itch-Relief-Ointment-1-Hydrocortisone-Anti-Itch-Ointment-1-Oz-Tube/1598170819.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing (3 pack) Aquaphor Healing Balm Stick, 0.65 oz (listing 15374315224). Ingredients block sat under a collapsed section; expanded and read. Variant match: 3-pack. Cross-check: brand site text Petrolatum (30%) matches the active. Verbatim keeps the Active/Inactive label and the Purpose tag as printed. Other listings checked before this one: Walmart 0.65 oz Pack of 3 (7455005955), which the earlier pass reported with no ingredients block; not re-checked. Note: the Walmart listing is a 3-pack, and the Amazon and Walgreens listings found are single 0.65 oz sticks, not used. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart (3 pack) - https://www.walmart.com/ip/3-pack-Aquaphor-Healing-Balm-Stick-Skin-Protectant-0-65-Oz-Stick/15374315224.</t>
+          <t>Audit notes: Walmart listing (3 pack) Aquaphor Healing Balm Stick, 0.65 oz (listing 15374315224). Ingredients block sat under a collapsed section; expanded and read. Variant match: 3-pack. Cross-check: brand site text Petrolatum (30%) matches the active. Verbatim keeps the Active/Inactive label and the Purpose tag as printed. Other listings checked before this one: Walmart 0.65 oz Pack of 3 (7455005955), which the earlier pass reported with no ingredients block; not re-checked. Note: the Walmart listing is a 3-pack, and the Amazon and Walgreens listings found are single 0.65 oz sticks, not used. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Balm Stick (0.65oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 4 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart (3 pack) - https://www.walmart.com/ip/3-pack-Aquaphor-Healing-Balm-Stick-Skin-Protectant-0-65-Oz-Stick/15374315224.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Audit notes: CVS listing Aquaphor Advanced Therapy Repairing Foot Masks, 1 Pair (prodid 648998). CVS shows the full list under Active Ingredients (uppercase) and Inactive Ingredients (title case); both contain the same 24 items in the same order. Title-case Inactive list used verbatim. Cross-check: first three (Water, Glycerin, Urea) match brand site. Target listing (0.7 fl oz) was not used; CVS 1-pair listing taken as the match for the brand row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-advanced-therapy-repairing-foot-masks-1-pair-prodid-648998.</t>
+          <t>Audit notes: CVS listing Aquaphor Advanced Therapy Repairing Foot Masks, 1 Pair (prodid 648998). CVS shows the full list under Active Ingredients (uppercase) and Inactive Ingredients (title case); both contain the same 24 items in the same order. Title-case Inactive list used verbatim. Cross-check: first three (Water, Glycerin, Urea) match brand site. Target listing (0.7 fl oz) was not used; CVS 1-pair listing taken as the match for the brand row. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 11 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: CVS - https://www.cvs.com/shop/ingredients/aquaphor-advanced-therapy-repairing-foot-masks-1-pair-prodid-648998.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant For Dry and Cracked Skin, 1.75 oz. Tube'. Cross-check: active Petrolatum (41%) matches brand site. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Skin-Protectant-For-Dry-and-Cracked-Skin-1-75-oz-Tube/761757933.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Audit notes: Amazon listing Aquaphor Advanced Therapy Ointment Body Spray, 6.2 OZ, Pack of 1 (B07TR75W9H). Variant match on size 6.2 oz. Cross-check: first three (Butane, Petrolatum, Mineral Oil) match brand site. CVS (3.7 oz) and Walmart (3.7 oz) listings were not used as they are a different size. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 3 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon - https://www.amazon.com/dp/B07TR75W9H.</t>
+          <t>Audit notes: Amazon listing Aquaphor Advanced Therapy Ointment Body Spray, 6.2 OZ, Pack of 1 (B07TR75W9H). Variant match on size 6.2 oz. Cross-check: first three (Butane, Petrolatum, Mineral Oil) match brand site. CVS (3.7 oz) and Walmart (3.7 oz) listings were not used as they are a different size. D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 3 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Amazon - https://www.amazon.com/dp/B07TR75W9H.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor® Children's Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor Healing Ointment Skin Protectant, Fragrance Free, 14 oz Jar'. Cross-check: active Petrolatum (41%) matches brand site. Identical printed text on 1 other product(s): Aquaphor® Children's Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Healing-Ointment-Advanced-Therapy-Skin-Protectant-for-Dry-Compromised-Skin-14-oz-Jar/10810942.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Audit notes: Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from grade (2026-10-17; replaces D7 and D8). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609.</t>
+          <t>Audit notes: Walmart listing 'Aquaphor, Healing Ointment for Dry Skin, Fragrance Free, 7 oz'. Cross-check: brand-site active Petrolatum (41%) matches first listed retailer ingredient. Identical printed text on 1 other product(s): Aquaphor® Baby Healing Ointment (14oz.). D6: glycerin is a caution ingredient (not a flag); it floors a Puberty Safe product at Use Caution. 2 unknown ingredient(s) excluded from flags (2026-10-17). D3: bisabolol counted as a full flag (cat. 4); no chamomile oil or extract listed in this product. Ingredient source: Walmart - https://www.walmart.com/ip/Aquaphor-Advanced-Therapy-Healing-Ointment-Skin-Protectant-7-oz/45800609.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
